--- a/media/data/program_ICAAM_2026.xlsx
+++ b/media/data/program_ICAAM_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bahcesehir-my.sharepoint.com/personal/charyyar_ashyralyyev_bau_edu_tr/Documents/Belgeler/Charyyar/Conference/Conference2026/ICAAM2026/Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="708" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54983579-1F81-40B6-AC57-2964E9118A51}"/>
+  <xr:revisionPtr revIDLastSave="786" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D69697F-1487-431E-9537-192610D207F9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="145">
   <si>
     <t xml:space="preserve">  HALL  Miramor Hotel&amp;Spa</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Authors and Title of the Talk</t>
-  </si>
-  <si>
-    <t>Allaberen Ashyralyev</t>
   </si>
   <si>
     <t>12.00-12.15</t>
@@ -167,20 +164,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Kordan Ospanov, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Maximal regularity conditions of the solution of a second-order differential equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Arsen Pskhu, </t>
     </r>
     <r>
@@ -222,21 +205,6 @@
         <charset val="162"/>
       </rPr>
       <t>Discreteness of the spectrum of a high-order difference operator</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Murat Sultanov (Bakytbek Sarsenov, Yerkebulan Nurlanuly, Merey Abdukadyrova), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Numerical solution of the inverse coefficient problem for an elliptic equation</t>
     </r>
   </si>
   <si>
@@ -310,20 +278,6 @@
   </si>
   <si>
     <r>
-      <t>Zhailan Salavatovna Tutkusheva,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A new approach to finding global extrema of multivariable objective functions</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Medet Jumadildayev (Saule Abdykassymova), </t>
     </r>
     <r>
@@ -713,12 +667,38 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>Guldara Aubakirova (Makhmud Sadybekov)</t>
+      <t xml:space="preserve">Nurlan Temirbekov (A. Kerimakyn, A.K. Muratova), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mathematical methods for processing geological data and forecasting prospective ore-bearing areas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nurgul Sairam, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Spectral properties of a second-order differential operator with the spectral parameter in the boundary conditions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Batirkhan Turmetov (Ainur Shalkhar),</t>
     </r>
     <r>
       <rPr>
@@ -728,41 +708,7 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>, On an inverse problem for the Poisson equation with an even source term</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Nurlan Temirbekov (A. Kerimakyn, A.K. Muratova), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mathematical methods for processing geological data and forecasting prospective ore-bearing areas</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Nurgul Sairam, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Spectral properties of a second-order differential operator with the spectral parameter in the boundary conditions</t>
+      <t xml:space="preserve"> On a time nonlocal problem for a polyharmonic equation with involution</t>
     </r>
   </si>
   <si>
@@ -775,7 +721,7 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t xml:space="preserve">Nihan Aliyev, </t>
+      <t xml:space="preserve">Dounia Belakroum, </t>
     </r>
     <r>
       <rPr>
@@ -785,22 +731,7 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>Solution of a nonlocal problem with boundary conditions for homogeneous ordinary differential equation with continuously varying first order derivatives</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Batirkhan Turmetov (Ainur Shalkhar),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve"> On a time nonlocal problem for a polyharmonic equation with involution</t>
+      <t>Existence and Uniqueness for a Variable-Order Fractional $p(\cdot)$-Laplacian Equation with a Causal Delay Term</t>
     </r>
   </si>
   <si>
@@ -813,7 +744,259 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t xml:space="preserve">Dounia Belakroum, </t>
+      <t>Moldir Shazyndayeva,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>An inverse problem for time fractional pseudo-parabolic equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Dinara Altynbek (Batirkhan Turmetov),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On a generalization of the Robin problem for a nonlocal analogue of the Poisson equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Alexandre Soldatov</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>The Riemann-Hilbert problem for first-order elliptic systems in piecewise smooth domains</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve">Kheireddine Belakroum (Allaberen Ashyralyev), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Stability analysis of some third-order partial differential equations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dilek Kuzali Bürücü,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Data-Driven Modeling and Low-Rank Approximation of the Dielectric Response of PVC Prepared under Electric Fields </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Akbota Abylayeva  (Ryskul Oinarov,  Askar Baiarystan),  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Two-weight estimates for integral operators  with power-logarithmic singularities, p &gt; q </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ezgi Soykan Ürün (Allaberen Ashyralyev, Maksat Ashyraliyev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Stability analysis for advection–diffusion equations and their numerical approximations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ali Ugur Sazaklioglu (Tuğba Akman), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>On the numerical solution of an inverse source problem by model order reduction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bakytbek Koshanov,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Riemann-Hilbert problem for a fourth-order elliptic equation in a quadrant</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dinara Sarsenaly (Ainur Temirkhanova),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The oscillatory of one class of the high-order Sturm-Liouville difference equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Yasar Sozen  (Allaberen Ashyralyev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A note on interpolation spaces generated by the second order differential operator with dependent coefficient and Samarskii-İonkin conditions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vladimir Matveev, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>On smoothness of isometries</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mizhda Abbas Headayat (Faraidun K. Hamasalh, Twana Abbas Hidayat), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>A new non-polynomial fractional hyperbolic spline approach with convergence study for fractional Fredholm integro-differential equations</t>
+    </r>
+  </si>
+  <si>
+    <t>18.00-19.00</t>
+  </si>
+  <si>
+    <t>Yaşar Sözen</t>
+  </si>
+  <si>
+    <t>Ozgur Yildirim</t>
+  </si>
+  <si>
+    <t>Makhmud Sadybekov</t>
+  </si>
+  <si>
+    <t>Durvudkhan Suragan</t>
+  </si>
+  <si>
+    <t>Ravshan Ashurov</t>
+  </si>
+  <si>
+    <t>Bilal Bilalov</t>
+  </si>
+  <si>
+    <t>Alexander Meskhi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Andrey Muravnik (Russia)
+</t>
     </r>
     <r>
       <rPr>
@@ -823,7 +1006,335 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>Existence and Uniqueness for a Variable-Order Fractional $p(\cdot)$-Laplacian Equation with a Causal Delay Term</t>
+      <t xml:space="preserve"> Series expansions of solutions of initial-value problems for hyperbolic differential-difference equations: computational aspects</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Alexander Meskhi (Georgia), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Multilinear Rellich and Hardy inequalities</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Bilal Bilalov (Azerbaijan),           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>On Applications of the Concept of $\otimes$-Basis in Approximation Theory and Partial Differential Equations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Virginia Kiryakova (Bulgaria), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve">Generalized fractional integrals related to Le Roy-, Feinman integrals- and Rathie $İ$-generalized hypergeometric functions </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:  Prof. Dr. Alexander L. Skubachevskii (Russia),
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Global solutions of the Cauchy problem for the Vlasov-Poisson system and plasma confinement</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr.   Ljubisa D. R. Kocinac (Serbia), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>On sequential Karamata theory</t>
+    </r>
+  </si>
+  <si>
+    <t>Bahaddin Sinsoysal</t>
+  </si>
+  <si>
+    <t>Nurlan Temirbekov</t>
+  </si>
+  <si>
+    <r>
+      <t>Ainur Kabulova,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Solution of forward and inverse problems for the convection–diffusion–reaction equation using neural networks</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Atif Namazov, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Optimal parameter identification of a discrete gas-lift process</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Jamilya Jumabaeva (Erlan Nursultanov),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Anisotropic Morrey spaces and the boundedness of the Riesz operator in them</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Telman Gasymov (İlkin Feyzullayev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On the strong solvability of the Laplace equation with a non-classical boundary condition</t>
+    </r>
+  </si>
+  <si>
+    <t>Charyyar Ashyralyyev</t>
+  </si>
+  <si>
+    <r>
+      <t>Ozgur Yildirim (Allaberen Ashyralyev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On the asymptotic and uniform difference schemes for hyperbolic perturbation problems</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Muvasharkhan Jenaliyev (Kadyrbek Sharipov),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On a family of spectral problems for fourth-order ODE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dinmukhammed Akpan, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Construction of regular conservation laws for Nijenhuis operators</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Alexander Rogovoy, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>On singular solutions of one boundary value problem with an internal condition for the Lavrent'ev-Bitsadze equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Atirgul Kydyrbaikyzy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, On the integral representation of regular solutions to the heat equation and boundary conditions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ekrem Savas (Rabia Savas),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> İ-lacunary statistical convergence in partial metric spaces</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mersaid Aripov (Mitsuru Sugimoto, Madina Khojimurodova),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Finite propagation, localization, and self-similar behavior of degenerate nonlinear cross-diffusion systems with variable coefficients</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Erlan Nursultanov</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Net spaces and applications</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Arshyn Altybay,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Wave equation driven by mixed local-nonlocal operators with singular coefficients</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nurlan İmanbaev (Makhmud Sadybekov),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Unconditional basis property of root functions of the operator of multiple differentiation on a segment with a spectral parameter in one boundary condition</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Nedyu Popivanov (Bulgaria), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Pohozhaev identities and applications for mixed type equations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Durvudkhan Suragan,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Geometric Hardy inequalities on the Heisenberg group and applications</t>
+    </r>
+  </si>
+  <si>
+    <t>Arsen Pskhu</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mahir Rasulov (B.Sinsoysal), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve">Solution of a nonlocal problem with boundary conditions
+for a homogeneous ordinary differential equation with
+continuously varying second-order derivatives
+</t>
     </r>
   </si>
   <si>
@@ -836,7 +1347,7 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>Guliya Mussabayeva,</t>
+      <t xml:space="preserve">Öykü Yener (Nihan Aliyev, Natiq Ibragimov), </t>
     </r>
     <r>
       <rPr>
@@ -846,7 +1357,71 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t xml:space="preserve"> On the Fourier transform of functions from the mixed-metric Lorentz spaces L_{\overline{2},\overline{r}}</t>
+      <t>On a method of transferring of non-local boundary value problem for ordinary differential equations of the first order to the Cauchy problem</t>
+    </r>
+  </si>
+  <si>
+    <t>11.00-11.30</t>
+  </si>
+  <si>
+    <t>13.00-13.15</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mesut Urun (Allaberen Ashyralyev), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Stable Difference Schemes for Time-Dependent Source Identification in the Schrodinger Equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Charyyar Ashyralyyev, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Absolute stable difference scheme for numerical solving source identification  elliptic problem with nonlocal condition</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Murat Sultanov (Bakytbek Sarsenov, Yerkebulan Nurlanuly, Bakytbek Sarsenov), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Numerical solution of the inverse coefficient problem for an elliptic equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nihan Aliyev, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Solution of a nonlocal problem with boundary conditions for a homogeneous ordinary differential equation with continuously varying first order derivatives</t>
     </r>
   </si>
   <si>
@@ -859,97 +1434,7 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>Moldir Shazyndayeva,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>An inverse problem for time fractional pseudo-parabolic equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Dinara Altynbek (Batirkhan Turmetov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On a generalization of the Robin problem for a nonlocal analogue of the Poisson equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Alexandre Soldatov</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Riemann-Hilbert problem for first-order elliptic systems in piecewise smooth domains</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Kheireddine Belakroum (Allaberen Ashyralyev), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Stability analysis of some third-order partial differential equations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Assanova Rysbiike (Kasenov Syrym), </t>
+      <t xml:space="preserve">Guldara Aubakirova (Makhmud Sadybekov),  </t>
     </r>
     <r>
       <rPr>
@@ -959,12 +1444,12 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>A gradient-based approach to the inverse thermoacoustic problem using quaternion Fourier transform</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Kasenov Syrym (Tleulesova Aigerim, Dauletbay Moldir), </t>
+      <t xml:space="preserve"> Inverse Source Problems for the Poisson Equation in a Disk</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Farrukh Mukhamedov, </t>
     </r>
     <r>
       <rPr>
@@ -974,58 +1459,12 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>Numerical solution of two-dimensional magnetotelluric inverse problems using Nesterov's accelerated gradient method</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Dilek Kuzali Bürücü,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Data-Driven Modeling and Low-Rank Approximation of the Dielectric Response of PVC Prepared under Electric Fields </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Akbota Abylayeva  (Ryskul Oinarov,  Askar Baiarystan),  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Two-weight estimates for integral operators  with power-logarithmic singularities, p &gt; q </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ezgi Soykan Ürün (Allaberen Ashyralyev, Maksat Ashyraliyev),</t>
+      <t>Historic Behavior for a Lotka-Volterra Operators on the simplex</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Zhailan Salavatovna Tutkusheva,</t>
     </r>
     <r>
       <rPr>
@@ -1033,12 +1472,12 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Stability analysis for advection–diffusion equations and their numerical approximations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ali Ugur Sazaklioglu (Tuğba Akman), </t>
+      <t xml:space="preserve"> A new approach to finding global extrema of multivariable objective functions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kordan Ospanov, </t>
     </r>
     <r>
       <rPr>
@@ -1046,102 +1485,12 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t>On the numerical solution of an inverse source problem by model order reduction</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Bakytbek Koshanov,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Riemann-Hilbert problem for a fourth-order elliptic equation in a quadrant</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Dinara Sarsenaly (Ainur Temirkhanova),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> The oscillatory of one class of the high-order Sturm-Liouville difference equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Yasar Sozen  (Allaberen Ashyralyev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A note on interpolation spaces generated by the second order differential operator with dependent coefficient and Samarskii-İonkin conditions</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Vladimir Matveev, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>On smoothness of isometries</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mizhda Abbas Headayat (Faraidun K. Hamasalh, Twana Abbas Hidayat), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>A new non-polynomial fractional hyperbolic spline approach with convergence study for fractional Fredholm integro-differential equations</t>
-    </r>
-  </si>
-  <si>
-    <t>18.00-19.00</t>
-  </si>
-  <si>
-    <t>Yaşar Sözen</t>
-  </si>
-  <si>
-    <t>Ozgur Yildirim</t>
-  </si>
-  <si>
-    <t>Makhmud Sadybekov</t>
-  </si>
-  <si>
-    <t>Durvudkhan Suragan</t>
-  </si>
-  <si>
-    <t>Ravshan Ashurov</t>
-  </si>
-  <si>
-    <t>Bilal Bilalov</t>
-  </si>
-  <si>
-    <t>Alexander Meskhi</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Andrey Muravnik (Russia)
-</t>
+      <t>Maximal regularity conditions of the solution of a second-order differential equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sergey Tikhonov, </t>
     </r>
     <r>
       <rPr>
@@ -1151,27 +1500,12 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t xml:space="preserve"> Series expansions of solutions of initial-value problems for hyperbolic differential-difference equations: computational aspects</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Alexander Meskhi (Georgia), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Multilinear Rellich and Hardy inequalities</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Bilal Bilalov (Azerbaijan),           </t>
+      <t>New Fourier inequalities</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Armend Shabani, </t>
     </r>
     <r>
       <rPr>
@@ -1181,318 +1515,7 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>On Applications of the Concept of $\otimes$-Basis in Approximation Theory and Partial Differential Equations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Virginia Kiryakova (Bulgaria), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Generalized fractional integrals related to Le Roy-, Feinman integrals- and Rathie $İ$-generalized hypergeometric functions </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:  Prof. Dr. Alexander L. Skubachevskii (Russia),
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Global solutions of the Cauchy problem for the Vlasov-Poisson system and plasma confinement</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr.   Ljubisa D. R. Kocinac (Serbia), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>On sequential Karamata theory</t>
-    </r>
-  </si>
-  <si>
-    <t>Bahaddin Sinsoysal</t>
-  </si>
-  <si>
-    <t>Nurlan Temirbekov</t>
-  </si>
-  <si>
-    <r>
-      <t>Ainur Kabulova,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Solution of forward and inverse problems for the convection–diffusion–reaction equation using neural networks</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Myrzagali Ospanov (Akerke Merzetkhan, Oleksandr Stanzhytskyi),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On the solvability of a problem for a nonlinear pseudoparabolic equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Atif Namazov, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Optimal parameter identification of a discrete gas-lift process</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Jamilya Jumabaeva (Erlan Nursultanov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Anisotropic Morrey spaces and the boundedness of the Riesz operator in them</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Telman Gasymov (İlkin Feyzullayev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On the strong solvability of the Laplace equation with a non-classical boundary condition</t>
-    </r>
-  </si>
-  <si>
-    <t>Charyyar Ashyralyyev</t>
-  </si>
-  <si>
-    <r>
-      <t>Ozgur Yildirim (Allaberen Ashyralyev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On the asymptotic and uniform difference schemes for hyperbolic perturbation problems</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Muvasharkhan Jenaliyev (Kadyrbek Sharipov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On a family of spectral problems for fourth-order ODE</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dinmukhammed Akpan, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Construction of regular conservation laws for Nijenhuis operators</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Alexander Rogovoy, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>On singular solutions of one boundary value problem with an internal condition for the Lavrent'ev-Bitsadze equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Atirgul Kydyrbaikyzy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>, On the integral representation of regular solutions to the heat equation and boundary conditions</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ekrem Savas (Rabia Savas),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> İ-lacunary statistical convergence in partial metric spaces</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mersaid Aripov (Mitsuru Sugimoto, Madina Khojimurodova),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Finite propagation, localization, and self-similar behavior of degenerate nonlinear cross-diffusion systems with variable coefficients</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Erlan Nursultanov</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>, Net spaces and applications</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Arshyn Altybay,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Wave equation driven by mixed local-nonlocal operators with singular coefficients</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Nurlan İmanbaev (Makhmud Sadybekov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Unconditional basis property of root functions of the operator of multiple differentiation on a segment with a spectral parameter in one boundary condition</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Nedyu Popivanov (Bulgaria), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Pohozhaev identities and applications for mixed type equations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Durvudkhan Suragan,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Geometric Hardy inequalities on the Heisenberg group and applications</t>
-    </r>
-  </si>
-  <si>
-    <t>Arsen Pskhu</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mahir Rasulov (B.Sinsoysal), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Solution of a nonlocal problem with boundary conditions
-for a homogeneous ordinary differential equation with
-continuously varying second-order derivatives
-</t>
+      <t>Subword Pattern Statistics in Carlitz and Palindromic Compositions</t>
     </r>
   </si>
   <si>
@@ -1505,7 +1528,7 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t xml:space="preserve">Öykü Yener (Nihan Aliyev, Natiq Ibragimov), </t>
+      <t>Igor Miroshnichenko (Nadezhda Bondareva, Azamat Safiullin)</t>
     </r>
     <r>
       <rPr>
@@ -1515,55 +1538,108 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>On a method of transferring of non-local boundary value problem for ordinary differential equations of the first order to the Cauchy problem</t>
-    </r>
-  </si>
-  <si>
-    <t>11.00-11.30</t>
-  </si>
-  <si>
-    <t>13.00-13.15</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mesut Urun (Allaberen Ashyralyev), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Stable Difference Schemes for Time-Dependent Source Identification in the Schrodinger Equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Charyyar Ashyralyyev, </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">, Mathematical modeling of heat transfer in hollow building blocks with internal partitions </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="162"/>
-      </rPr>
-      <t>Absolute stable difference scheme for numerical solving source identification  elliptic problem with nonlocal condition</t>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Abdullatif Yalcin, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Boundedness and Integral Inequalities for Sonin-Type Fractional Integral Operators on Morrey Spaces </t>
+    </r>
+  </si>
+  <si>
+    <t>Allabere Ashyralyev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charyyar Ashyralyyev </t>
+  </si>
+  <si>
+    <t>Maksat Ashyraliyev</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Matyokub Bakoev, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Probabilistic representation and Monte Carlo solution of initial--boundary value problems for the advection--diffusion  equation in air pollution modelling </t>
+    </r>
+  </si>
+  <si>
+    <t>13.15-15.00</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Dauren Matin, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Pre-compactness of sets in the discrete Morrey-type spaces </t>
     </r>
   </si>
   <si>
     <t>Program of Eighth International Conference on Analysis and Applied Mathematics (ICAAM2026)
 Antalya,  Miramor Hotel&amp;Spa
 September 26 - October 3,  2026
- (Updated 16.09.2026 )</t>
+ (Updated 17.09.2026 )</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1763,8 +1839,16 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1805,6 +1889,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1967,7 +2057,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2038,9 +2128,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2059,11 +2146,14 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2072,24 +2162,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2124,8 +2221,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2376,8 +2472,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>138</v>
+      <c r="A1" s="52" t="s">
+        <v>144</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
@@ -2388,26 +2484,26 @@
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>42</v>
+      <c r="A3" s="53" t="s">
+        <v>41</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
+      <c r="A4" s="55"/>
       <c r="B4" s="34"/>
       <c r="C4" s="34"/>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
-        <v>25</v>
+      <c r="A5" s="54" t="s">
+        <v>24</v>
       </c>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="55" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="34"/>
@@ -2426,171 +2522,171 @@
     </row>
     <row r="8" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="53" t="s">
-        <v>4</v>
+        <v>22</v>
+      </c>
+      <c r="B8" s="56" t="s">
+        <v>140</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="54"/>
+        <v>23</v>
+      </c>
+      <c r="B9" s="57"/>
       <c r="C9" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="48"/>
+        <v>12</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="51"/>
     </row>
     <row r="11" spans="1:3" ht="43" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>51</v>
+        <v>13</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="24" t="s">
-        <v>43</v>
+        <v>14</v>
+      </c>
+      <c r="B12" s="57"/>
+      <c r="C12" s="28" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="29" t="s">
-        <v>94</v>
+        <v>18</v>
+      </c>
+      <c r="B13" s="57"/>
+      <c r="C13" s="28" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="29" t="s">
-        <v>95</v>
+        <v>19</v>
+      </c>
+      <c r="B14" s="57"/>
+      <c r="C14" s="28" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="29" t="s">
-        <v>96</v>
+        <v>15</v>
+      </c>
+      <c r="B15" s="57"/>
+      <c r="C15" s="28" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="48"/>
+        <v>16</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="51"/>
     </row>
     <row r="17" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>90</v>
+        <v>17</v>
+      </c>
+      <c r="B17" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="29" t="s">
-        <v>91</v>
+        <v>4</v>
+      </c>
+      <c r="B18" s="57"/>
+      <c r="C18" s="28" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="29" t="s">
-        <v>92</v>
+        <v>6</v>
+      </c>
+      <c r="B19" s="57"/>
+      <c r="C19" s="28" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="29" t="s">
-        <v>93</v>
+        <v>31</v>
+      </c>
+      <c r="B20" s="57"/>
+      <c r="C20" s="28" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="29" t="s">
-        <v>136</v>
+        <v>27</v>
+      </c>
+      <c r="B21" s="60"/>
+      <c r="C21" s="16" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="45"/>
+        <v>125</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="44" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="45"/>
+        <v>28</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="48"/>
     </row>
     <row r="24" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="56"/>
+      <c r="C24" s="59"/>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="45"/>
+        <v>88</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="48"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3563,7 +3659,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C960"/>
+  <dimension ref="A1:C961"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6328125" customWidth="1"/>
@@ -3573,14 +3669,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -3598,155 +3694,163 @@
     </row>
     <row r="4" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="58"/>
+        <v>23</v>
+      </c>
+      <c r="B5" s="37"/>
       <c r="C5" s="16" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="37"/>
+        <v>12</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="40"/>
     </row>
     <row r="7" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>124</v>
+        <v>13</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="56.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="42"/>
-      <c r="C8" s="30" t="s">
-        <v>125</v>
+      <c r="C8" s="29" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="42"/>
-      <c r="C9" s="30" t="s">
-        <v>126</v>
+      <c r="C9" s="29" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="42"/>
-      <c r="C10" s="30" t="s">
-        <v>127</v>
+      <c r="C10" s="29" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="43"/>
-      <c r="C11" s="30" t="s">
-        <v>128</v>
+      <c r="C11" s="29" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="37"/>
+        <v>16</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="40"/>
     </row>
     <row r="13" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>119</v>
+        <v>17</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="30" t="s">
-        <v>120</v>
+        <v>4</v>
+      </c>
+      <c r="B14" s="45"/>
+      <c r="C14" s="29" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="30" t="s">
-        <v>121</v>
+        <v>6</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="29" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="30" t="s">
-        <v>122</v>
+        <v>31</v>
+      </c>
+      <c r="B16" s="45"/>
+      <c r="C16" s="29" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="45"/>
+      <c r="C17" s="29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="45.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="46"/>
+      <c r="C18" s="28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="40"/>
+    </row>
+    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="37"/>
-    </row>
-    <row r="19" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="B20" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="32"/>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C20" s="38"/>
+    </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4687,17 +4791,18 @@
     <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:B11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B13:B18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4719,14 +4824,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -4744,162 +4849,162 @@
     </row>
     <row r="4" spans="1:3" ht="53" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>104</v>
+        <v>22</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>95</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="40"/>
+        <v>32</v>
+      </c>
+      <c r="B5" s="61"/>
       <c r="C5" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="40"/>
+        <v>33</v>
+      </c>
+      <c r="B6" s="61"/>
       <c r="C6" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="37"/>
+        <v>12</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="40"/>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>99</v>
+        <v>13</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>90</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="59"/>
+        <v>14</v>
+      </c>
+      <c r="B9" s="45"/>
       <c r="C9" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="59"/>
+        <v>18</v>
+      </c>
+      <c r="B10" s="45"/>
       <c r="C10" s="16" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="59"/>
+        <v>19</v>
+      </c>
+      <c r="B11" s="45"/>
       <c r="C11" s="16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="59.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="60"/>
+        <v>15</v>
+      </c>
+      <c r="B12" s="62"/>
       <c r="C12" s="16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="40"/>
+    </row>
+    <row r="14" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="37"/>
-    </row>
-    <row r="14" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>111</v>
+      <c r="B14" s="41" t="s">
+        <v>102</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="40"/>
+        <v>4</v>
+      </c>
+      <c r="B15" s="61"/>
       <c r="C15" s="16" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="43" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="40"/>
+        <v>6</v>
+      </c>
+      <c r="B16" s="61"/>
       <c r="C16" s="16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="40"/>
+        <v>31</v>
+      </c>
+      <c r="B17" s="61"/>
       <c r="C17" s="16" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="41"/>
+        <v>27</v>
+      </c>
+      <c r="B18" s="46"/>
       <c r="C18" s="8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="37"/>
+        <v>28</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="40"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="32"/>
+      <c r="C20" s="38"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5874,14 +5979,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -5899,159 +6004,162 @@
     </row>
     <row r="4" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>102</v>
+        <v>22</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>93</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="40"/>
+        <v>32</v>
+      </c>
+      <c r="B5" s="61"/>
       <c r="C5" s="21" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="40"/>
+        <v>33</v>
+      </c>
+      <c r="B6" s="61"/>
       <c r="C6" s="16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="37"/>
+      <c r="A7" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="40"/>
     </row>
     <row r="8" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>112</v>
+        <v>13</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>103</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="40"/>
+        <v>14</v>
+      </c>
+      <c r="B9" s="61"/>
       <c r="C9" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="40"/>
+        <v>18</v>
+      </c>
+      <c r="B10" s="61"/>
       <c r="C10" s="16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="21" t="s">
-        <v>67</v>
+        <v>19</v>
+      </c>
+      <c r="B11" s="61"/>
+      <c r="C11" s="16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="46"/>
+      <c r="C12" s="21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="37"/>
+      <c r="B13" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="40"/>
     </row>
     <row r="14" spans="1:3" ht="50.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>9</v>
+        <v>17</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>8</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" s="42"/>
       <c r="C16" s="8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="42"/>
-      <c r="C17" s="25" t="s">
-        <v>68</v>
+      <c r="C17" s="24" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="46" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="43"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="37"/>
+      <c r="B19" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="40"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="32"/>
+      <c r="C20" s="38"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7026,14 +7134,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -7051,162 +7159,162 @@
     </row>
     <row r="4" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>101</v>
+        <v>22</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>92</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="40"/>
+        <v>32</v>
+      </c>
+      <c r="B5" s="61"/>
       <c r="C5" s="16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="25" t="s">
-        <v>74</v>
+        <v>33</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="24" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="37"/>
+        <v>12</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="40"/>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>6</v>
+        <v>13</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="58"/>
+        <v>14</v>
+      </c>
+      <c r="B9" s="37"/>
       <c r="C9" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="26.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="8" t="s">
-        <v>75</v>
+        <v>18</v>
+      </c>
+      <c r="B10" s="37"/>
+      <c r="C10" s="31" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="58"/>
+        <v>19</v>
+      </c>
+      <c r="B11" s="37"/>
       <c r="C11" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="58"/>
+        <v>15</v>
+      </c>
+      <c r="B12" s="37"/>
       <c r="C12" s="8" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="37"/>
+        <v>16</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="40"/>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>85</v>
+        <v>17</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="40"/>
+        <v>4</v>
+      </c>
+      <c r="B15" s="61"/>
       <c r="C15" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="40"/>
+        <v>6</v>
+      </c>
+      <c r="B16" s="61"/>
       <c r="C16" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="40"/>
+        <v>31</v>
+      </c>
+      <c r="B17" s="61"/>
       <c r="C17" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="25" t="s">
-        <v>88</v>
+        <v>27</v>
+      </c>
+      <c r="B18" s="46"/>
+      <c r="C18" s="24" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="37"/>
+        <v>28</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="40"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="32"/>
+      <c r="C20" s="38"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8181,14 +8289,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -8206,162 +8314,162 @@
     </row>
     <row r="4" spans="1:3" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>103</v>
+        <v>22</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>94</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="40"/>
+        <v>32</v>
+      </c>
+      <c r="B5" s="61"/>
       <c r="C5" s="16" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="25" t="s">
-        <v>76</v>
+        <v>33</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="24" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="37"/>
+        <v>12</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="40"/>
     </row>
     <row r="8" spans="1:3" ht="48.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>118</v>
+        <v>13</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>108</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="46" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="25" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="24" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="40"/>
+        <v>18</v>
+      </c>
+      <c r="B10" s="61"/>
       <c r="C10" s="16" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="40"/>
+        <v>19</v>
+      </c>
+      <c r="B11" s="61"/>
       <c r="C11" s="16" t="s">
-        <v>47</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="41"/>
+        <v>15</v>
+      </c>
+      <c r="B12" s="46"/>
       <c r="C12" s="16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="37"/>
+        <v>16</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="40"/>
     </row>
     <row r="14" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="61" t="s">
-        <v>111</v>
+        <v>17</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>102</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="29.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="16" t="s">
-        <v>61</v>
+        <v>4</v>
+      </c>
+      <c r="B15" s="64"/>
+      <c r="C15" s="21" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="62"/>
+        <v>6</v>
+      </c>
+      <c r="B16" s="64"/>
       <c r="C16" s="16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="62"/>
+        <v>31</v>
+      </c>
+      <c r="B17" s="64"/>
       <c r="C17" s="16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="63"/>
+        <v>27</v>
+      </c>
+      <c r="B18" s="65"/>
       <c r="C18" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="37"/>
+        <v>28</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="40"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="32"/>
+      <c r="C20" s="38"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9326,7 +9434,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C952"/>
+  <dimension ref="A1:D953"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6328125" customWidth="1"/>
@@ -9334,21 +9442,21 @@
     <col min="3" max="3" width="48.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
     </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
@@ -9359,87 +9467,96 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="66" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="25" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="69"/>
+      <c r="C5" s="24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="69"/>
+      <c r="C6" s="24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="25" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="67"/>
+      <c r="B7" s="69"/>
       <c r="C7" s="16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="47.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="69"/>
+      <c r="C8" s="16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="67"/>
-      <c r="C8" s="16" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="33.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="69"/>
+      <c r="C9" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="67"/>
-      <c r="C9" s="25" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="68"/>
-      <c r="C10" s="25" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="65" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="24"/>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10376,12 +10493,13 @@
     <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B4:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>

--- a/media/data/program_ICAAM_2026.xlsx
+++ b/media/data/program_ICAAM_2026.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bahcesehir-my.sharepoint.com/personal/charyyar_ashyralyyev_bau_edu_tr/Documents/Belgeler/Charyyar/Conference/Conference2026/ICAAM2026/Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="786" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D69697F-1487-431E-9537-192610D207F9}"/>
+  <xr:revisionPtr revIDLastSave="966" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F988F3B1-C78B-44B8-822C-1E3EDD36A51D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="September 27" sheetId="1" r:id="rId1"/>
-    <sheet name="September 28" sheetId="9" r:id="rId2"/>
-    <sheet name="September 29" sheetId="10" r:id="rId3"/>
-    <sheet name="September 30" sheetId="12" r:id="rId4"/>
-    <sheet name="October 1" sheetId="13" r:id="rId5"/>
-    <sheet name="October 2" sheetId="14" r:id="rId6"/>
-    <sheet name="October 3" sheetId="15" r:id="rId7"/>
+    <sheet name="September 26" sheetId="16" r:id="rId1"/>
+    <sheet name="September 27" sheetId="1" r:id="rId2"/>
+    <sheet name="September 28" sheetId="9" r:id="rId3"/>
+    <sheet name="September 29" sheetId="10" r:id="rId4"/>
+    <sheet name="September 30" sheetId="12" r:id="rId5"/>
+    <sheet name="October 1" sheetId="13" r:id="rId6"/>
+    <sheet name="October 2" sheetId="14" r:id="rId7"/>
+    <sheet name="October 3" sheetId="15" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="158">
   <si>
     <t xml:space="preserve">  HALL  Miramor Hotel&amp;Spa</t>
   </si>
@@ -95,12 +96,6 @@
   </si>
   <si>
     <t>Best paper award &amp; Closing ceremony</t>
-  </si>
-  <si>
-    <t>Opening Speech 
- Prof.Dr. Allaberen Ashyralyev (Türkiye),
-Prof.Dr.Michael Ruzhansky (Belgium), 
-Prof.Dr.Makhmud Sadybekov (Kazakhstan)</t>
   </si>
   <si>
     <t>9.00-9.30</t>
@@ -481,21 +476,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Deniz Ağirseven (Yusuf Ensar Demirci), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Heat transfer model with involution: analytical approaches and FDM analysis</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Abdulgafur Taşkin (Allaberen Ashyralyev),</t>
     </r>
     <r>
@@ -664,26 +644,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Nurlan Temirbekov (A. Kerimakyn, A.K. Muratova), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mathematical methods for processing geological data and forecasting prospective ore-bearing areas</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Nurgul Sairam, </t>
     </r>
     <r>
@@ -767,6 +727,29 @@
   </si>
   <si>
     <r>
+      <t>Alexandre Soldatov</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>The Riemann-Hilbert problem for first-order elliptic systems in piecewise smooth domains</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <b/>
         <sz val="10"/>
@@ -775,7 +758,7 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>Dinara Altynbek (Batirkhan Turmetov),</t>
+      <t xml:space="preserve">Kheireddine Belakroum (Allaberen Ashyralyev), </t>
     </r>
     <r>
       <rPr>
@@ -784,12 +767,12 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> On a generalization of the Robin problem for a nonlocal analogue of the Poisson equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Alexandre Soldatov</t>
+      <t>Stability analysis of some third-order partial differential equations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dilek Kuzali Bürücü,</t>
     </r>
     <r>
       <rPr>
@@ -798,7 +781,7 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -807,20 +790,285 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t>The Riemann-Hilbert problem for first-order elliptic systems in piecewise smooth domains</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t xml:space="preserve">Data-Driven Modeling and Low-Rank Approximation of the Dielectric Response of PVC Prepared under Electric Fields </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Akbota Abylayeva  (Ryskul Oinarov,  Askar Baiarystan),  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Two-weight estimates for integral operators  with power-logarithmic singularities, p &gt; q </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ezgi Soykan Ürün (Allaberen Ashyralyev, Maksat Ashyraliyev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Stability analysis for advection–diffusion equations and their numerical approximations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ali Ugur Sazaklioglu (Tuğba Akman), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>On the numerical solution of an inverse source problem by model order reduction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bakytbek Koshanov,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Riemann-Hilbert problem for a fourth-order elliptic equation in a quadrant</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dinara Sarsenaly (Ainur Temirkhanova),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The oscillatory of one class of the high-order Sturm-Liouville difference equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Yasar Sozen  (Allaberen Ashyralyev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A note on interpolation spaces generated by the second order differential operator with dependent coefficient and Samarskii-İonkin conditions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vladimir Matveev, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>On smoothness of isometries</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mizhda Abbas Headayat (Faraidun K. Hamasalh, Twana Abbas Hidayat), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>A new non-polynomial fractional hyperbolic spline approach with convergence study for fractional Fredholm integro-differential equations</t>
+    </r>
+  </si>
+  <si>
+    <t>18.00-19.00</t>
+  </si>
+  <si>
+    <t>Yaşar Sözen</t>
+  </si>
+  <si>
+    <t>Ozgur Yildirim</t>
+  </si>
+  <si>
+    <t>Makhmud Sadybekov</t>
+  </si>
+  <si>
+    <t>Durvudkhan Suragan</t>
+  </si>
+  <si>
+    <t>Ravshan Ashurov</t>
+  </si>
+  <si>
+    <t>Bilal Bilalov</t>
+  </si>
+  <si>
+    <t>Alexander Meskhi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Andrey Muravnik (Russia)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve"> Series expansions of solutions of initial-value problems for hyperbolic differential-difference equations: computational aspects</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Alexander Meskhi (Georgia), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Multilinear Rellich and Hardy inequalities</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Bilal Bilalov (Azerbaijan),           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>On Applications of the Concept of $\otimes$-Basis in Approximation Theory and Partial Differential Equations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Virginia Kiryakova (Bulgaria), </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t xml:space="preserve">Kheireddine Belakroum (Allaberen Ashyralyev), </t>
+      <t xml:space="preserve">Generalized fractional integrals related to Le Roy-, Feinman integrals- and Rathie $İ$-generalized hypergeometric functions </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr.   Ljubisa D. R. Kocinac (Serbia), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>On sequential Karamata theory</t>
+    </r>
+  </si>
+  <si>
+    <t>Bahaddin Sinsoysal</t>
+  </si>
+  <si>
+    <r>
+      <t>Ainur Kabulova,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Solution of forward and inverse problems for the convection–diffusion–reaction equation using neural networks</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Atif Namazov, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Optimal parameter identification of a discrete gas-lift process</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Jamilya Jumabaeva (Erlan Nursultanov),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Anisotropic Morrey spaces and the boundedness of the Riesz operator in them</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Telman Gasymov (İlkin Feyzullayev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On the strong solvability of the Laplace equation with a non-classical boundary condition</t>
+    </r>
+  </si>
+  <si>
+    <t>Charyyar Ashyralyyev</t>
+  </si>
+  <si>
+    <r>
+      <t>Ozgur Yildirim (Allaberen Ashyralyev),</t>
     </r>
     <r>
       <rPr>
@@ -829,21 +1077,12 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t>Stability analysis of some third-order partial differential equations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Dilek Kuzali Bürücü,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> On the asymptotic and uniform difference schemes for hyperbolic perturbation problems</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Muvasharkhan Jenaliyev (Kadyrbek Sharipov),</t>
     </r>
     <r>
       <rPr>
@@ -852,21 +1091,12 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Data-Driven Modeling and Low-Rank Approximation of the Dielectric Response of PVC Prepared under Electric Fields </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Akbota Abylayeva  (Ryskul Oinarov,  Askar Baiarystan),  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> On a family of spectral problems for fourth-order ODE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dinmukhammed Akpan, </t>
     </r>
     <r>
       <rPr>
@@ -875,281 +1105,12 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Two-weight estimates for integral operators  with power-logarithmic singularities, p &gt; q </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ezgi Soykan Ürün (Allaberen Ashyralyev, Maksat Ashyraliyev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Stability analysis for advection–diffusion equations and their numerical approximations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ali Ugur Sazaklioglu (Tuğba Akman), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>On the numerical solution of an inverse source problem by model order reduction</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Bakytbek Koshanov,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Riemann-Hilbert problem for a fourth-order elliptic equation in a quadrant</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Dinara Sarsenaly (Ainur Temirkhanova),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> The oscillatory of one class of the high-order Sturm-Liouville difference equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Yasar Sozen  (Allaberen Ashyralyev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A note on interpolation spaces generated by the second order differential operator with dependent coefficient and Samarskii-İonkin conditions</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Vladimir Matveev, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>On smoothness of isometries</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mizhda Abbas Headayat (Faraidun K. Hamasalh, Twana Abbas Hidayat), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>A new non-polynomial fractional hyperbolic spline approach with convergence study for fractional Fredholm integro-differential equations</t>
-    </r>
-  </si>
-  <si>
-    <t>18.00-19.00</t>
-  </si>
-  <si>
-    <t>Yaşar Sözen</t>
-  </si>
-  <si>
-    <t>Ozgur Yildirim</t>
-  </si>
-  <si>
-    <t>Makhmud Sadybekov</t>
-  </si>
-  <si>
-    <t>Durvudkhan Suragan</t>
-  </si>
-  <si>
-    <t>Ravshan Ashurov</t>
-  </si>
-  <si>
-    <t>Bilal Bilalov</t>
-  </si>
-  <si>
-    <t>Alexander Meskhi</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Andrey Muravnik (Russia)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve"> Series expansions of solutions of initial-value problems for hyperbolic differential-difference equations: computational aspects</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Alexander Meskhi (Georgia), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Multilinear Rellich and Hardy inequalities</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Bilal Bilalov (Azerbaijan),           </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>On Applications of the Concept of $\otimes$-Basis in Approximation Theory and Partial Differential Equations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Virginia Kiryakova (Bulgaria), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Generalized fractional integrals related to Le Roy-, Feinman integrals- and Rathie $İ$-generalized hypergeometric functions </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:  Prof. Dr. Alexander L. Skubachevskii (Russia),
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Global solutions of the Cauchy problem for the Vlasov-Poisson system and plasma confinement</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr.   Ljubisa D. R. Kocinac (Serbia), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>On sequential Karamata theory</t>
-    </r>
-  </si>
-  <si>
-    <t>Bahaddin Sinsoysal</t>
-  </si>
-  <si>
-    <t>Nurlan Temirbekov</t>
-  </si>
-  <si>
-    <r>
-      <t>Ainur Kabulova,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Solution of forward and inverse problems for the convection–diffusion–reaction equation using neural networks</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Atif Namazov, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Optimal parameter identification of a discrete gas-lift process</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Jamilya Jumabaeva (Erlan Nursultanov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Anisotropic Morrey spaces and the boundedness of the Riesz operator in them</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Telman Gasymov (İlkin Feyzullayev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On the strong solvability of the Laplace equation with a non-classical boundary condition</t>
-    </r>
-  </si>
-  <si>
-    <t>Charyyar Ashyralyyev</t>
-  </si>
-  <si>
-    <r>
-      <t>Ozgur Yildirim (Allaberen Ashyralyev),</t>
+      <t>Construction of regular conservation laws for Nijenhuis operators</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Alexander Rogovoy, </t>
     </r>
     <r>
       <rPr>
@@ -1158,63 +1119,7 @@
         <rFont val="Aptos"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> On the asymptotic and uniform difference schemes for hyperbolic perturbation problems</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Muvasharkhan Jenaliyev (Kadyrbek Sharipov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On a family of spectral problems for fourth-order ODE</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dinmukhammed Akpan, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Construction of regular conservation laws for Nijenhuis operators</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Alexander Rogovoy, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
       <t>On singular solutions of one boundary value problem with an internal condition for the Lavrent'ev-Bitsadze equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Atirgul Kydyrbaikyzy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>, On the integral representation of regular solutions to the heat equation and boundary conditions</t>
     </r>
   </si>
   <si>
@@ -1396,21 +1301,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Murat Sultanov (Bakytbek Sarsenov, Yerkebulan Nurlanuly, Bakytbek Sarsenov), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Numerical solution of the inverse coefficient problem for an elliptic equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Nihan Aliyev, </t>
     </r>
     <r>
@@ -1567,12 +1457,6 @@
     </r>
   </si>
   <si>
-    <t>Allabere Ashyralyev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charyyar Ashyralyyev </t>
-  </si>
-  <si>
     <t>Maksat Ashyraliyev</t>
   </si>
   <si>
@@ -1601,9 +1485,6 @@
     </r>
   </si>
   <si>
-    <t>13.15-15.00</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1632,14 +1513,255 @@
     <t>Program of Eighth International Conference on Analysis and Applied Mathematics (ICAAM2026)
 Antalya,  Miramor Hotel&amp;Spa
 September 26 - October 3,  2026
- (Updated 17.09.2026 )</t>
+ (Updated 18.09.2026 )</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Murat Sultanov Makhmud Sadybekov, Yerkebulan Nurlanuly, Bakytbek Sarsenov), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Numerical solution of the inverse coefficient problem for an elliptic equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sabina Sadigova, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve"> Basicity of the Sine and Cosine Systems in Weighted Sobolev Spaces </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Yeter Farhadova,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Maximal F-Regularity of an Abstract Cauchy Problem with Sectorial Operators </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yusuf Ensar Demirci (Deniz Ağirseven), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Heat transfer model with involution: analytical approaches and FDM analysis</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrey Muravnik  </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Robyn Irawan (Indonesia)  (Benny Yong, Erin Andrea Ramadhani Pramono, Neilshan Loedy, Farah Kristiani) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Age-structured Bayesian SIR modelling with reversible-jump MCMC: a comparative study of two social contact matrix projections </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:  Prof. Dr. Alexander L. Skubachevskii (Russia), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Global solutions of the Cauchy problem for the Vlasov-Poisson system and plasma confinement</t>
+    </r>
+  </si>
+  <si>
+    <t>13.00-14.00</t>
+  </si>
+  <si>
+    <t>14.00-14.15</t>
+  </si>
+  <si>
+    <t>14.15-14.30</t>
+  </si>
+  <si>
+    <t>14.30-14.45</t>
+  </si>
+  <si>
+    <t>14.45-15.00</t>
+  </si>
+  <si>
+    <r>
+      <t>Atirgul Kydyrbaikyzy (Tynysbek Kalmenov)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, On the integral representation of regular solutions to the heat equation and boundary conditions</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deniz Agirseven</t>
+  </si>
+  <si>
+    <t>Ali Yakar</t>
+  </si>
+  <si>
+    <t>Allaberen Ashyralyev</t>
+  </si>
+  <si>
+    <t>15.00-15.15</t>
+  </si>
+  <si>
+    <t>15.15-18.00</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A. Arif Ergin, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">30 Years of Applied Mathematics for Radar Signature Computation </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ali Yakar  (Mohammed Ahmed Issa Alhussein) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">The ITD approach in quasilinearization of integro-differential equations   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Aigerim Kalizhanova  (Bruce Pell,  Aisha Tursynkozha, Denise Dengi, Ardak Kashkynbayev, Yang Kuang) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Modeling Tumor-Immune Dynamics: Synergistic Combination Treatment and the Role of Dynamic PD-L1 Regulation  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dinara Altynbek (Batirkhan Turmetov),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On a generalization of the Robin problem for a nonlocal analogue of the Poisson equation</t>
+    </r>
+  </si>
+  <si>
+    <t>Opening Speech 
+Dean of Faculty Engineering and Natural Science
+Bahçeşehir University,Türkiye,  Prof.Dr. Arif Engin
+Prof.Dr. Allaberen Ashyralyev (Chair ICAAM2026,Türkiye),
+Prof.Dr.Michael Ruzhansky (Chair ICAAM2026,Belgium), 
+Prof.Dr.Makhmud Sadybekov (Chair ICAAM2026, Kazakhstan)</t>
+  </si>
+  <si>
+    <t>13.15-15.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1847,8 +1969,29 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="1"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1889,12 +2032,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor rgb="FFF3F3F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2057,7 +2194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2146,13 +2283,10 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2186,7 +2320,15 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2198,16 +2340,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2220,8 +2353,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2229,21 +2362,24 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2260,6 +2396,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>615950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Resim 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43CFF193-0D2D-CB36-0401-40DB84E515F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="1911350"/>
+          <a:ext cx="5359399" cy="6489700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2459,11 +2650,1220 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5247BF-11E7-4D0E-8712-45710F639C07}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.6328125" customWidth="1"/>
+    <col min="3" max="3" width="44.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+    </row>
+    <row r="4" spans="1:3" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="47"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C966"/>
+  <dimension ref="A1:C962"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="52"/>
+    </row>
+    <row r="8" spans="1:3" ht="77.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="55"/>
+      <c r="C9" s="28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="55"/>
+      <c r="C11" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="55"/>
+      <c r="C12" s="28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="52"/>
+    </row>
+    <row r="14" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="55"/>
+      <c r="C15" s="28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="55"/>
+      <c r="C16" s="28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="55"/>
+      <c r="C17" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="49"/>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="49"/>
+    </row>
+    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="57"/>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="49"/>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B14:B17"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" location="success" display="Opening Speech _x000a_Dean of Faculty Engineering and Natural Science_x000a_Bahcesehir University,  Prof.Dr. Arif Engin_x000a_Prof.Dr. Allaberen Ashyralyev,_x000a_Prof.Dr.Michael Ruzhansky, _x000a_Prof.Dr.Makhmud Sadybekov" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91965B31-E9D2-4C5A-B708-D756E08C9A18}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:C965"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6328125" customWidth="1"/>
@@ -2471,223 +3871,229 @@
     <col min="3" max="3" width="48.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="39"/>
+    </row>
+    <row r="7" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="56.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="41"/>
+      <c r="C9" s="29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="27.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="41"/>
+      <c r="C10" s="29" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="42"/>
+      <c r="C11" s="29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="39"/>
+    </row>
+    <row r="13" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="44"/>
+      <c r="C15" s="29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="45.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="44"/>
+      <c r="C17" s="29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="39"/>
+    </row>
+    <row r="19" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="51"/>
-    </row>
-    <row r="11" spans="1:3" ht="43" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="28" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="51"/>
-    </row>
-    <row r="17" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="56" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="48"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="68" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="44"/>
+      <c r="C22" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="44"/>
+      <c r="C23" s="21" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="24" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="58" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="59"/>
-    </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="48"/>
-    </row>
+      <c r="C24" s="37"/>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3628,1188 +5034,25 @@
     <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B17:B21"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" location="success" display="Opening Speech _x000a_Dean of Faculty Engineering and Natural Science_x000a_Bahcesehir University,  Prof.Dr. Arif Engin_x000a_Prof.Dr. Allaberen Ashyralyev,_x000a_Prof.Dr.Michael Ruzhansky, _x000a_Prof.Dr.Makhmud Sadybekov" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91965B31-E9D2-4C5A-B708-D756E08C9A18}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:C961"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.6328125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
-    <col min="3" max="3" width="48.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="40"/>
-    </row>
-    <row r="7" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="56.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="29" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="29" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="40"/>
-    </row>
-    <row r="13" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="29" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="45.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="29" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="45.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="40"/>
-    </row>
-    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="38"/>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:B11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="B19:B23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D48DAA0E-4626-4AB9-A8B6-CA57ABB497BD}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4823,18 +5066,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
+      <c r="A1" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -4849,162 +5092,162 @@
     </row>
     <row r="4" spans="1:3" ht="53" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>95</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="61"/>
+        <v>31</v>
+      </c>
+      <c r="B5" s="58"/>
       <c r="C5" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="61"/>
+        <v>32</v>
+      </c>
+      <c r="B6" s="58"/>
       <c r="C6" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="40"/>
+      <c r="C7" s="39"/>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>90</v>
+      <c r="B8" s="40" t="s">
+        <v>97</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="45"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="45"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="59.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="62"/>
+      <c r="B12" s="60"/>
       <c r="C12" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="40"/>
+      <c r="C13" s="39"/>
     </row>
     <row r="14" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>102</v>
+      <c r="B14" s="40" t="s">
+        <v>86</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="61"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="43" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="61"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="61"/>
+        <v>30</v>
+      </c>
+      <c r="B17" s="58"/>
       <c r="C17" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="8" t="s">
-        <v>74</v>
+        <v>26</v>
+      </c>
+      <c r="B18" s="59"/>
+      <c r="C18" s="28" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="40"/>
+      <c r="C19" s="39"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="38"/>
+      <c r="C20" s="37"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5964,7 +6207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD4E71A-4601-41AB-9D69-E00C644D183E}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5978,18 +6221,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
+      <c r="A1" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -6004,162 +6247,162 @@
     </row>
     <row r="4" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="41" t="s">
-        <v>93</v>
+        <v>21</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>89</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="61"/>
+        <v>31</v>
+      </c>
+      <c r="B5" s="58"/>
       <c r="C5" s="21" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="61"/>
+        <v>32</v>
+      </c>
+      <c r="B6" s="58"/>
       <c r="C6" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="40"/>
+      <c r="C7" s="39"/>
     </row>
     <row r="8" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>103</v>
+      <c r="B8" s="40" t="s">
+        <v>8</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="61"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="61"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="61"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="46"/>
+      <c r="B12" s="42"/>
       <c r="C12" s="21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="40"/>
-    </row>
-    <row r="14" spans="1:3" ht="50.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="39"/>
+    </row>
+    <row r="14" spans="1:3" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>8</v>
+      <c r="B14" s="40" t="s">
+        <v>138</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="42"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="42"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="42"/>
+        <v>30</v>
+      </c>
+      <c r="B17" s="41"/>
       <c r="C17" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="46" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="30" t="s">
-        <v>106</v>
+        <v>26</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="24" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="40"/>
+      <c r="C19" s="39"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="38"/>
+      <c r="C20" s="37"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7119,7 +7362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2005CD-206D-4CAE-8092-43ECDA1AF9DE}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -7133,18 +7376,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
+      <c r="A1" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -7159,1317 +7402,162 @@
     </row>
     <row r="4" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="41" t="s">
-        <v>92</v>
+        <v>21</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>88</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="61"/>
+        <v>31</v>
+      </c>
+      <c r="B5" s="58"/>
       <c r="C5" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="61"/>
+        <v>32</v>
+      </c>
+      <c r="B6" s="58"/>
       <c r="C6" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="40"/>
+      <c r="C7" s="39"/>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="35" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="37"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="26.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="31" t="s">
-        <v>130</v>
+      <c r="B10" s="36"/>
+      <c r="C10" s="8" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="37"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="37"/>
+      <c r="B12" s="36"/>
       <c r="C12" s="8" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="40"/>
-    </row>
-    <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="39"/>
+    </row>
+    <row r="14" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>78</v>
+      <c r="B14" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="61"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="61"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="61"/>
+        <v>30</v>
+      </c>
+      <c r="B17" s="58"/>
       <c r="C17" s="8" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="46"/>
+        <v>26</v>
+      </c>
+      <c r="B18" s="59"/>
       <c r="C18" s="24" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="40"/>
+      <c r="C19" s="39"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="38"/>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B4:B6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D7B7B7-1E0B-4DAC-8C06-1D4E18E61472}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:C961"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.6328125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
-    <col min="3" max="3" width="48.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="40"/>
-    </row>
-    <row r="8" spans="1:3" ht="48.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="46" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="40"/>
-    </row>
-    <row r="14" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="29.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="40"/>
-    </row>
-    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="38"/>
+      <c r="C20" s="37"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9430,11 +8518,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCDFB74-DF65-46AC-BCEF-D8E6AE12706A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D7B7B7-1E0B-4DAC-8C06-1D4E18E61472}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D953"/>
+  <dimension ref="A1:D962"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6328125" customWidth="1"/>
@@ -9443,18 +8531,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
+      <c r="A1" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -9467,93 +8555,1264 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="68" t="s">
-        <v>138</v>
+        <v>21</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="58"/>
+      <c r="C5" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="58"/>
+      <c r="C6" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="30"/>
+    </row>
+    <row r="7" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="39"/>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="58"/>
+      <c r="C9" s="24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="58"/>
+      <c r="C10" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="58"/>
+      <c r="C11" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="39"/>
+    </row>
+    <row r="14" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="62"/>
+      <c r="C16" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="62"/>
+      <c r="C18" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="27.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="69"/>
+      <c r="C19" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="39"/>
+    </row>
+    <row r="21" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="37"/>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B14:B19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCDFB74-DF65-46AC-BCEF-D8E6AE12706A}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:D954"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="3" max="3" width="48.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>149</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="69"/>
+        <v>39</v>
+      </c>
+      <c r="B5" s="65"/>
       <c r="C5" s="24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="24" t="s">
-        <v>107</v>
+        <v>31</v>
+      </c>
+      <c r="B6" s="65"/>
+      <c r="C6" s="25" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="69"/>
+        <v>32</v>
+      </c>
+      <c r="B7" s="65"/>
       <c r="C7" s="16" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="69"/>
+      <c r="B8" s="65"/>
       <c r="C8" s="16" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="65"/>
+      <c r="C9" s="31" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="69"/>
-      <c r="C10" s="32" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="B10" s="65"/>
+      <c r="C10" s="31" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="31" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="D11" s="24"/>
-    </row>
-    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="66"/>
+      <c r="C12" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="30"/>
+    </row>
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C13" s="64" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10494,12 +10753,13 @@
     <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B4:B11"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B4:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>

--- a/media/data/program_ICAAM_2026.xlsx
+++ b/media/data/program_ICAAM_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bahcesehir-my.sharepoint.com/personal/charyyar_ashyralyyev_bau_edu_tr/Documents/Belgeler/Charyyar/Conference/Conference2026/ICAAM2026/Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="966" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F988F3B1-C78B-44B8-822C-1E3EDD36A51D}"/>
+  <xr:revisionPtr revIDLastSave="1040" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9883E058-4F80-4B11-A2D1-557A7907F58E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -491,20 +491,6 @@
   </si>
   <si>
     <r>
-      <t>Makhpal Manarbek (Nazerke Tleukhanova),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Survey of Grand Spaces</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="10"/>
@@ -1208,20 +1194,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Durvudkhan Suragan,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Geometric Hardy inequalities on the Heisenberg group and applications</t>
-    </r>
-  </si>
-  <si>
     <t>Arsen Pskhu</t>
   </si>
   <si>
@@ -1656,20 +1628,6 @@
   </si>
   <si>
     <t>15.15-18.00</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A. Arif Ergin, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">30 Years of Applied Mathematics for Radar Signature Computation </t>
-    </r>
   </si>
   <si>
     <r>
@@ -1729,20 +1687,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Dinara Altynbek (Batirkhan Turmetov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On a generalization of the Robin problem for a nonlocal analogue of the Poisson equation</t>
     </r>
   </si>
   <si>
@@ -1755,6 +1699,61 @@
   </si>
   <si>
     <t>13.15-15.00</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A. Arif Ergin, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">30 years of applied mathematics for radar signature computation </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Durvudkhan Suragan,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The nonlinear Hausdorff-Young inequality</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Makhpal Manarbek (Nazerke Tleukhanova),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Bochkarev type inequalities in anisotropic grand Lorentz spaces</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kairat Usmanov,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A Functional Parameterization Method for a Nonlocal Boundary Value Problem with Involution</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2035,65 +2034,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2111,276 +2057,136 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2403,15 +2209,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>615950</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>30976</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:colOff>418170</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>755651</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2440,8 +2246,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1" y="1911350"/>
-          <a:ext cx="5359399" cy="6489700"/>
+          <a:off x="0" y="30976"/>
+          <a:ext cx="5761463" cy="6346748"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2651,45 +2457,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5247BF-11E7-4D0E-8712-45710F639C07}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.6328125" customWidth="1"/>
     <col min="3" max="3" width="44.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+    <row r="1" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="24"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+    </row>
+    <row r="29" spans="1:4" ht="71" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+    </row>
+    <row r="31" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-    </row>
-    <row r="4" spans="1:3" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A31:D31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2707,193 +2514,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>156</v>
+      <c r="B5" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="9" t="s">
-        <v>96</v>
+      <c r="B6" s="26"/>
+      <c r="C6" s="6" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:3" ht="77.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>139</v>
+      <c r="B8" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="28" t="s">
-        <v>125</v>
+      <c r="B9" s="26"/>
+      <c r="C9" s="16" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="28" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="26"/>
+      <c r="C11" s="16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="28" t="s">
+    <row r="12" spans="1:3" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="16" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="28" t="s">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="29"/>
+    </row>
+    <row r="14" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="26"/>
+      <c r="C16" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="26"/>
+      <c r="C17" s="16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="29"/>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="29"/>
+    </row>
+    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="38"/>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="52"/>
-    </row>
-    <row r="14" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="28" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="49"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="49"/>
-    </row>
-    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="56" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="57"/>
-    </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="49"/>
+      <c r="C21" s="29"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3872,226 +3679,226 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B4" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="29"/>
+    </row>
+    <row r="7" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="56.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="29"/>
+    </row>
+    <row r="13" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="26"/>
+      <c r="C16" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="45.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="26"/>
+      <c r="C17" s="17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="29"/>
+    </row>
+    <row r="19" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="39"/>
-    </row>
-    <row r="7" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="56.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="29" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="27.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="29" t="s">
+      <c r="B19" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="26"/>
+      <c r="C20" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="26"/>
+      <c r="C21" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="26"/>
+      <c r="C22" s="17" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="39"/>
-    </row>
-    <row r="13" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="40" t="s">
+    <row r="23" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="29" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="29" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="45.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="29" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="39"/>
-    </row>
-    <row r="19" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B19" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="28" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="68" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="29" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="21" t="s">
-        <v>155</v>
+      <c r="B23" s="26"/>
+      <c r="C23" s="11" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B24" s="35" t="s">
+      <c r="A24" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="37"/>
+      <c r="C24" s="27"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5066,188 +4873,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="53" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>95</v>
+      <c r="B4" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="32"/>
+      <c r="C5" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="32"/>
+      <c r="C6" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="39"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="26"/>
+      <c r="C9" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="59.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="60"/>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="6" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="39"/>
+      <c r="C13" s="29"/>
     </row>
     <row r="14" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>123</v>
+      <c r="B14" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="16" t="s">
+      <c r="B15" s="32"/>
+      <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="43" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="32"/>
+      <c r="C16" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="16" t="s">
+      <c r="B17" s="32"/>
+      <c r="C17" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="59"/>
-      <c r="C18" s="28" t="s">
-        <v>124</v>
+      <c r="B18" s="32"/>
+      <c r="C18" s="16" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="39"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6221,188 +6028,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>94</v>
+      <c r="B4" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="21" t="s">
-        <v>113</v>
+      <c r="B5" s="32"/>
+      <c r="C5" s="11" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="16" t="s">
-        <v>63</v>
+      <c r="B6" s="32"/>
+      <c r="C6" s="6" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="39"/>
-    </row>
-    <row r="8" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="C7" s="29"/>
+    </row>
+    <row r="8" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>137</v>
+      <c r="C8" s="19" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="25"/>
+      <c r="C9" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="21" t="s">
-        <v>73</v>
+      <c r="B12" s="25"/>
+      <c r="C12" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="39"/>
+      <c r="C13" s="29"/>
     </row>
     <row r="14" spans="1:3" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="25"/>
+      <c r="C15" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="24" t="s">
-        <v>62</v>
+      <c r="B17" s="25"/>
+      <c r="C17" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="46" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="24" t="s">
-        <v>100</v>
+      <c r="B18" s="25"/>
+      <c r="C18" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="39"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7376,188 +7183,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>93</v>
+      <c r="B4" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="16" t="s">
-        <v>65</v>
+      <c r="B5" s="32"/>
+      <c r="C5" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="24" t="s">
-        <v>68</v>
+      <c r="B6" s="32"/>
+      <c r="C6" s="12" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="39"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="8" t="s">
-        <v>64</v>
+      <c r="B9" s="26"/>
+      <c r="C9" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="26.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="8" t="s">
-        <v>122</v>
+      <c r="B10" s="26"/>
+      <c r="C10" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="8" t="s">
-        <v>128</v>
+      <c r="B12" s="26"/>
+      <c r="C12" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="39"/>
+      <c r="C13" s="29"/>
     </row>
     <row r="14" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="32"/>
+      <c r="C16" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="32"/>
+      <c r="C17" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="8" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="59"/>
-      <c r="C18" s="24" t="s">
-        <v>75</v>
+      <c r="B18" s="32"/>
+      <c r="C18" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="39"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8531,198 +8338,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>92</v>
+      <c r="B4" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="16" t="s">
-        <v>115</v>
+      <c r="B5" s="32"/>
+      <c r="C5" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="24" t="s">
+      <c r="B6" s="32"/>
+      <c r="C6" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="29"/>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="30"/>
-    </row>
-    <row r="7" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="38" t="s">
+      <c r="C8" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="39"/>
-    </row>
-    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="24" t="s">
+      <c r="C13" s="29"/>
+    </row>
+    <row r="14" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="39"/>
+      <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="27.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="16" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="28" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="39"/>
-    </row>
-    <row r="14" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="27.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B20" s="43" t="s">
+      <c r="A20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="39"/>
+      <c r="C20" s="29"/>
     </row>
     <row r="21" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="37"/>
+      <c r="C21" s="27"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9696,124 +9503,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="67" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="24" t="s">
+      <c r="B4" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="12" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="25" t="s">
-        <v>74</v>
+      <c r="B6" s="42"/>
+      <c r="C6" s="13" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="65"/>
-      <c r="C7" s="16" t="s">
-        <v>120</v>
+      <c r="B7" s="42"/>
+      <c r="C7" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="65"/>
-      <c r="C8" s="16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="31" t="s">
+      <c r="B9" s="42"/>
+      <c r="C9" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="42"/>
+      <c r="C10" s="19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="19" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="65"/>
-      <c r="C10" s="31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="31" t="s">
-        <v>131</v>
-      </c>
-    </row>
     <row r="12" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="30"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="18"/>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="63" t="s">
+      <c r="A13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="64" t="s">
+      <c r="C13" s="23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="46"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+    </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/media/data/program_ICAAM_2026.xlsx
+++ b/media/data/program_ICAAM_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bahcesehir-my.sharepoint.com/personal/charyyar_ashyralyyev_bau_edu_tr/Documents/Belgeler/Charyyar/Conference/Conference2026/ICAAM2026/Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1040" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9883E058-4F80-4B11-A2D1-557A7907F58E}"/>
+  <xr:revisionPtr revIDLastSave="1067" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F40E0CF-BCEA-4487-9475-69AE35C69B2B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="September 26" sheetId="16" r:id="rId1"/>
@@ -22,8 +22,19 @@
     <sheet name="October 2" sheetId="14" r:id="rId7"/>
     <sheet name="October 3" sheetId="15" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="aVWS3Cp8ZhyYcqiZsuyBVFvLwIVUBqkS8qcwEZyqf+E="/>
     </ext>
@@ -32,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="152">
   <si>
     <t xml:space="preserve">  HALL  Miramor Hotel&amp;Spa</t>
   </si>
@@ -644,21 +655,6 @@
   </si>
   <si>
     <r>
-      <t>Batirkhan Turmetov (Ainur Shalkhar),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve"> On a time nonlocal problem for a polyharmonic equation with involution</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="10"/>
@@ -667,7 +663,176 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t xml:space="preserve">Dounia Belakroum, </t>
+      <t>Moldir Shazyndayeva,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>An inverse problem for time fractional pseudo-parabolic equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dilek Kuzali Bürücü,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Data-Driven Modeling and Low-Rank Approximation of the Dielectric Response of PVC Prepared under Electric Fields </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Akbota Abylayeva  (Ryskul Oinarov,  Askar Baiarystan),  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Two-weight estimates for integral operators  with power-logarithmic singularities, p &gt; q </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ezgi Soykan Ürün (Allaberen Ashyralyev, Maksat Ashyraliyev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Stability analysis for advection–diffusion equations and their numerical approximations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ali Ugur Sazaklioglu (Tuğba Akman), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>On the numerical solution of an inverse source problem by model order reduction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dinara Sarsenaly (Ainur Temirkhanova),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> The oscillatory of one class of the high-order Sturm-Liouville difference equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Yasar Sozen  (Allaberen Ashyralyev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A note on interpolation spaces generated by the second order differential operator with dependent coefficient and Samarskii-İonkin conditions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vladimir Matveev, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>On smoothness of isometries</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mizhda Abbas Headayat (Faraidun K. Hamasalh, Twana Abbas Hidayat), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>A new non-polynomial fractional hyperbolic spline approach with convergence study for fractional Fredholm integro-differential equations</t>
+    </r>
+  </si>
+  <si>
+    <t>18.00-19.00</t>
+  </si>
+  <si>
+    <t>Yaşar Sözen</t>
+  </si>
+  <si>
+    <t>Ozgur Yildirim</t>
+  </si>
+  <si>
+    <t>Makhmud Sadybekov</t>
+  </si>
+  <si>
+    <t>Ravshan Ashurov</t>
+  </si>
+  <si>
+    <t>Bilal Bilalov</t>
+  </si>
+  <si>
+    <t>Alexander Meskhi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Andrey Muravnik (Russia)
+</t>
     </r>
     <r>
       <rPr>
@@ -677,7 +842,288 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>Existence and Uniqueness for a Variable-Order Fractional $p(\cdot)$-Laplacian Equation with a Causal Delay Term</t>
+      <t xml:space="preserve"> Series expansions of solutions of initial-value problems for hyperbolic differential-difference equations: computational aspects</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Alexander Meskhi (Georgia), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Multilinear Rellich and Hardy inequalities</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Bilal Bilalov (Azerbaijan),           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>On Applications of the Concept of $\otimes$-Basis in Approximation Theory and Partial Differential Equations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Virginia Kiryakova (Bulgaria), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve">Generalized fractional integrals related to Le Roy-, Feinman integrals- and Rathie $İ$-generalized hypergeometric functions </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr.   Ljubisa D. R. Kocinac (Serbia), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>On sequential Karamata theory</t>
+    </r>
+  </si>
+  <si>
+    <t>Bahaddin Sinsoysal</t>
+  </si>
+  <si>
+    <r>
+      <t>Ainur Kabulova,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Solution of forward and inverse problems for the convection–diffusion–reaction equation using neural networks</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Atif Namazov, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Optimal parameter identification of a discrete gas-lift process</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Jamilya Jumabaeva (Erlan Nursultanov),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Anisotropic Morrey spaces and the boundedness of the Riesz operator in them</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Telman Gasymov (İlkin Feyzullayev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On the strong solvability of the Laplace equation with a non-classical boundary condition</t>
+    </r>
+  </si>
+  <si>
+    <t>Charyyar Ashyralyyev</t>
+  </si>
+  <si>
+    <r>
+      <t>Ozgur Yildirim (Allaberen Ashyralyev),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On the asymptotic and uniform difference schemes for hyperbolic perturbation problems</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Muvasharkhan Jenaliyev (Kadyrbek Sharipov),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> On a family of spectral problems for fourth-order ODE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dinmukhammed Akpan, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>Construction of regular conservation laws for Nijenhuis operators</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Alexander Rogovoy, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>On singular solutions of one boundary value problem with an internal condition for the Lavrent'ev-Bitsadze equation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ekrem Savas (Rabia Savas),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> İ-lacunary statistical convergence in partial metric spaces</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mersaid Aripov (Mitsuru Sugimoto, Madina Khojimurodova),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Finite propagation, localization, and self-similar behavior of degenerate nonlinear cross-diffusion systems with variable coefficients</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Erlan Nursultanov</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, Net spaces and applications</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Arshyn Altybay,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Wave equation driven by mixed local-nonlocal operators with singular coefficients</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nurlan İmanbaev (Makhmud Sadybekov),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Unconditional basis property of root functions of the operator of multiple differentiation on a segment with a spectral parameter in one boundary condition</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Nedyu Popivanov (Bulgaria), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Pohozhaev identities and applications for mixed type equations</t>
+    </r>
+  </si>
+  <si>
+    <t>Arsen Pskhu</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mahir Rasulov (B.Sinsoysal), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve">Solution of a nonlocal problem with boundary conditions
+for a homogeneous ordinary differential equation with
+continuously varying second-order derivatives
+</t>
     </r>
   </si>
   <si>
@@ -690,237 +1136,7 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t>Moldir Shazyndayeva,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>An inverse problem for time fractional pseudo-parabolic equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Alexandre Soldatov</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>The Riemann-Hilbert problem for first-order elliptic systems in piecewise smooth domains</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Kheireddine Belakroum (Allaberen Ashyralyev), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Stability analysis of some third-order partial differential equations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Dilek Kuzali Bürücü,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Data-Driven Modeling and Low-Rank Approximation of the Dielectric Response of PVC Prepared under Electric Fields </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Akbota Abylayeva  (Ryskul Oinarov,  Askar Baiarystan),  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Two-weight estimates for integral operators  with power-logarithmic singularities, p &gt; q </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ezgi Soykan Ürün (Allaberen Ashyralyev, Maksat Ashyraliyev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Stability analysis for advection–diffusion equations and their numerical approximations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ali Ugur Sazaklioglu (Tuğba Akman), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>On the numerical solution of an inverse source problem by model order reduction</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Bakytbek Koshanov,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Riemann-Hilbert problem for a fourth-order elliptic equation in a quadrant</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Dinara Sarsenaly (Ainur Temirkhanova),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> The oscillatory of one class of the high-order Sturm-Liouville difference equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Yasar Sozen  (Allaberen Ashyralyev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A note on interpolation spaces generated by the second order differential operator with dependent coefficient and Samarskii-İonkin conditions</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Vladimir Matveev, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>On smoothness of isometries</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mizhda Abbas Headayat (Faraidun K. Hamasalh, Twana Abbas Hidayat), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>A new non-polynomial fractional hyperbolic spline approach with convergence study for fractional Fredholm integro-differential equations</t>
-    </r>
-  </si>
-  <si>
-    <t>18.00-19.00</t>
-  </si>
-  <si>
-    <t>Yaşar Sözen</t>
-  </si>
-  <si>
-    <t>Ozgur Yildirim</t>
-  </si>
-  <si>
-    <t>Makhmud Sadybekov</t>
-  </si>
-  <si>
-    <t>Durvudkhan Suragan</t>
-  </si>
-  <si>
-    <t>Ravshan Ashurov</t>
-  </si>
-  <si>
-    <t>Bilal Bilalov</t>
-  </si>
-  <si>
-    <t>Alexander Meskhi</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Andrey Muravnik (Russia)
-</t>
+      <t xml:space="preserve">Öykü Yener (Nihan Aliyev, Natiq Ibragimov), </t>
     </r>
     <r>
       <rPr>
@@ -930,331 +1146,11 @@
         <family val="2"/>
         <charset val="162"/>
       </rPr>
-      <t xml:space="preserve"> Series expansions of solutions of initial-value problems for hyperbolic differential-difference equations: computational aspects</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Alexander Meskhi (Georgia), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Multilinear Rellich and Hardy inequalities</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Bilal Bilalov (Azerbaijan),           </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>On Applications of the Concept of $\otimes$-Basis in Approximation Theory and Partial Differential Equations</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Virginia Kiryakova (Bulgaria), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Generalized fractional integrals related to Le Roy-, Feinman integrals- and Rathie $İ$-generalized hypergeometric functions </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr.   Ljubisa D. R. Kocinac (Serbia), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>On sequential Karamata theory</t>
-    </r>
-  </si>
-  <si>
-    <t>Bahaddin Sinsoysal</t>
-  </si>
-  <si>
-    <r>
-      <t>Ainur Kabulova,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Solution of forward and inverse problems for the convection–diffusion–reaction equation using neural networks</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Atif Namazov, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Optimal parameter identification of a discrete gas-lift process</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Jamilya Jumabaeva (Erlan Nursultanov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Anisotropic Morrey spaces and the boundedness of the Riesz operator in them</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Telman Gasymov (İlkin Feyzullayev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On the strong solvability of the Laplace equation with a non-classical boundary condition</t>
-    </r>
-  </si>
-  <si>
-    <t>Charyyar Ashyralyyev</t>
-  </si>
-  <si>
-    <r>
-      <t>Ozgur Yildirim (Allaberen Ashyralyev),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On the asymptotic and uniform difference schemes for hyperbolic perturbation problems</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Muvasharkhan Jenaliyev (Kadyrbek Sharipov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> On a family of spectral problems for fourth-order ODE</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dinmukhammed Akpan, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Construction of regular conservation laws for Nijenhuis operators</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Alexander Rogovoy, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>On singular solutions of one boundary value problem with an internal condition for the Lavrent'ev-Bitsadze equation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ekrem Savas (Rabia Savas),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> İ-lacunary statistical convergence in partial metric spaces</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mersaid Aripov (Mitsuru Sugimoto, Madina Khojimurodova),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Finite propagation, localization, and self-similar behavior of degenerate nonlinear cross-diffusion systems with variable coefficients</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Erlan Nursultanov</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>, Net spaces and applications</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Arshyn Altybay,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Wave equation driven by mixed local-nonlocal operators with singular coefficients</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Nurlan İmanbaev (Makhmud Sadybekov),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Unconditional basis property of root functions of the operator of multiple differentiation on a segment with a spectral parameter in one boundary condition</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Invited Speaker:   Prof. Dr. Nedyu Popivanov (Bulgaria), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="3"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t>Pohozhaev identities and applications for mixed type equations</t>
-    </r>
-  </si>
-  <si>
-    <t>Arsen Pskhu</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mahir Rasulov (B.Sinsoysal), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Solution of a nonlocal problem with boundary conditions
-for a homogeneous ordinary differential equation with
-continuously varying second-order derivatives
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
-      <t xml:space="preserve">Öykü Yener (Nihan Aliyev, Natiq Ibragimov), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="162"/>
-      </rPr>
       <t>On a method of transferring of non-local boundary value problem for ordinary differential equations of the first order to the Cauchy problem</t>
     </r>
   </si>
   <si>
-    <t>11.00-11.30</t>
-  </si>
-  <si>
     <t>13.00-13.15</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mesut Urun (Allaberen Ashyralyev), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Stable Difference Schemes for Time-Dependent Source Identification in the Schrodinger Equation</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1754,6 +1650,12 @@
       </rPr>
       <t xml:space="preserve"> A Functional Parameterization Method for a Nonlocal Boundary Value Problem with Involution</t>
     </r>
+  </si>
+  <si>
+    <t>Bakytbek Koshanov,  Alexander Soldatov, Riemann-Hilbert problem for a fourth-order elliptic equation in a quadrant</t>
+  </si>
+  <si>
+    <t>10.15-10.45</t>
   </si>
 </sst>
 </file>
@@ -2061,7 +1963,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2099,9 +2001,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2123,28 +2022,10 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2152,19 +2033,50 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2173,20 +2085,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2461,32 +2359,32 @@
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.6328125" customWidth="1"/>
-    <col min="3" max="3" width="44.1796875" customWidth="1"/>
+    <col min="3" max="3" width="44.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-    </row>
-    <row r="29" spans="1:4" ht="71" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+    </row>
+    <row r="29" spans="1:4" ht="71.150000000000006" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-    </row>
-    <row r="31" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="45" t="s">
+      <c r="A30" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+    </row>
+    <row r="31" spans="1:4" ht="47.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2519,18 +2417,18 @@
       <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2547,160 +2445,160 @@
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>152</v>
+      <c r="B5" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="34"/>
     </row>
     <row r="8" spans="1:3" ht="77.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="41.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="16" t="s">
-        <v>123</v>
+      <c r="B9" s="39"/>
+      <c r="C9" s="15" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="39"/>
+      <c r="C10" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="32.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="16" t="s">
-        <v>81</v>
+      <c r="B11" s="39"/>
+      <c r="C11" s="15" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="16" t="s">
-        <v>82</v>
+      <c r="B12" s="39"/>
+      <c r="C12" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="29"/>
+      <c r="C13" s="34"/>
     </row>
     <row r="14" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>76</v>
+      <c r="B14" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="16" t="s">
-        <v>77</v>
+      <c r="B15" s="39"/>
+      <c r="C15" s="15" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="16" t="s">
-        <v>78</v>
+      <c r="B16" s="39"/>
+      <c r="C16" s="15" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="16" t="s">
-        <v>154</v>
+      <c r="B17" s="39"/>
+      <c r="C17" s="15" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="29"/>
+      <c r="C18" s="34"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="29"/>
-    </row>
-    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="38"/>
+      <c r="C20" s="41"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="29"/>
+      <c r="C21" s="34"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3679,18 +3577,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -3707,198 +3605,198 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>86</v>
+      <c r="B4" s="38" t="s">
+        <v>81</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="26"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="29"/>
-    </row>
-    <row r="7" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="34"/>
+    </row>
+    <row r="7" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>106</v>
+      <c r="B7" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="56.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="17" t="s">
-        <v>107</v>
+      <c r="B8" s="38"/>
+      <c r="C8" s="16" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="25"/>
+      <c r="B9" s="38"/>
       <c r="C9" s="6" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="17" t="s">
-        <v>108</v>
+      <c r="B10" s="38"/>
+      <c r="C10" s="16" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="17" t="s">
-        <v>110</v>
+      <c r="B11" s="38"/>
+      <c r="C11" s="16" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="29"/>
+      <c r="C12" s="34"/>
     </row>
     <row r="13" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>102</v>
+      <c r="B13" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="17" t="s">
-        <v>103</v>
+      <c r="B14" s="39"/>
+      <c r="C14" s="16" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="17" t="s">
-        <v>104</v>
+      <c r="B15" s="39"/>
+      <c r="C15" s="16" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="45.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="39"/>
+      <c r="C16" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="45.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="17" t="s">
-        <v>144</v>
+      <c r="B17" s="39"/>
+      <c r="C17" s="16" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="34"/>
+    </row>
+    <row r="19" spans="1:3" ht="39.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="39.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="16" t="s">
-        <v>150</v>
+        <v>133</v>
+      </c>
+      <c r="B20" s="39"/>
+      <c r="C20" s="15" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="20" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="38.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="17" t="s">
-        <v>109</v>
+        <v>135</v>
+      </c>
+      <c r="B22" s="39"/>
+      <c r="C22" s="16" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B23" s="26"/>
+        <v>140</v>
+      </c>
+      <c r="B23" s="39"/>
       <c r="C23" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="27"/>
+      <c r="C24" s="42"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4873,18 +4771,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -4897,22 +4795,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="53" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="53.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>90</v>
+      <c r="B4" s="38" t="s">
+        <v>84</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="32"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="6" t="s">
         <v>41</v>
       </c>
@@ -4921,7 +4819,7 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="23"/>
       <c r="C6" s="6" t="s">
         <v>42</v>
       </c>
@@ -4930,17 +4828,17 @@
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="34"/>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>96</v>
+      <c r="B8" s="38" t="s">
+        <v>90</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>51</v>
@@ -4950,7 +4848,7 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="6" t="s">
         <v>43</v>
       </c>
@@ -4959,7 +4857,7 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="6" t="s">
         <v>47</v>
       </c>
@@ -4968,7 +4866,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="26"/>
+      <c r="B11" s="39"/>
       <c r="C11" s="6" t="s">
         <v>59</v>
       </c>
@@ -4977,7 +4875,7 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="6" t="s">
         <v>60</v>
       </c>
@@ -4986,27 +4884,27 @@
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="29"/>
+      <c r="C13" s="34"/>
     </row>
     <row r="14" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>85</v>
+      <c r="B14" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="32"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
@@ -5015,7 +4913,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="32"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="6" t="s">
         <v>49</v>
       </c>
@@ -5024,7 +4922,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="32"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="6" t="s">
         <v>50</v>
       </c>
@@ -5033,28 +4931,28 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="16" t="s">
-        <v>122</v>
+      <c r="B18" s="23"/>
+      <c r="C18" s="15" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="29"/>
-    </row>
-    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="27"/>
+      <c r="C20" s="42"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6028,18 +5926,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -6056,65 +5954,65 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>88</v>
+      <c r="B4" s="38" t="s">
+        <v>82</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="32"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="11" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="23"/>
       <c r="C6" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="34"/>
     </row>
     <row r="8" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>127</v>
+      <c r="C8" s="18" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="25"/>
+      <c r="B9" s="38"/>
       <c r="C9" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="32.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="25"/>
+      <c r="B10" s="38"/>
       <c r="C10" s="6" t="s">
         <v>52</v>
       </c>
@@ -6123,7 +6021,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="25"/>
+      <c r="B11" s="38"/>
       <c r="C11" s="6" t="s">
         <v>56</v>
       </c>
@@ -6132,26 +6030,24 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="11" t="s">
-        <v>72</v>
-      </c>
+      <c r="B12" s="38"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="29"/>
-    </row>
-    <row r="14" spans="1:3" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="34"/>
+    </row>
+    <row r="14" spans="1:3" ht="42.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>136</v>
+      <c r="B14" s="38" t="s">
+        <v>128</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>54</v>
@@ -6161,7 +6057,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="25"/>
+      <c r="B15" s="38"/>
       <c r="C15" s="2" t="s">
         <v>65</v>
       </c>
@@ -6170,7 +6066,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="25"/>
+      <c r="B16" s="38"/>
       <c r="C16" s="2" t="s">
         <v>66</v>
       </c>
@@ -6179,7 +6075,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="25"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="12" t="s">
         <v>61</v>
       </c>
@@ -6188,28 +6084,28 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="25"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="29"/>
-    </row>
-    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="27"/>
+      <c r="C20" s="42"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7183,18 +7079,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -7207,22 +7103,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>87</v>
+      <c r="B4" s="38" t="s">
+        <v>95</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="26" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="26.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="32"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="6" t="s">
         <v>64</v>
       </c>
@@ -7231,7 +7127,7 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="23"/>
       <c r="C6" s="12" t="s">
         <v>67</v>
       </c>
@@ -7240,27 +7136,27 @@
       <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="34"/>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="38" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="39.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="2" t="s">
         <v>63</v>
       </c>
@@ -7269,63 +7165,63 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="26"/>
+      <c r="B11" s="39"/>
       <c r="C11" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="39.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="39.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="29"/>
-    </row>
-    <row r="14" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="34"/>
+    </row>
+    <row r="14" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>112</v>
+      <c r="B14" s="38" t="s">
+        <v>106</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="32"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="32"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="2" t="s">
         <v>44</v>
       </c>
@@ -7334,37 +7230,37 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="32"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="32"/>
+      <c r="B18" s="23"/>
       <c r="C18" s="12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="29"/>
-    </row>
-    <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="34"/>
+    </row>
+    <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="27"/>
+      <c r="C20" s="42"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8338,18 +8234,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -8362,61 +8258,61 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="42.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>89</v>
+      <c r="B4" s="38" t="s">
+        <v>83</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="32"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="23"/>
       <c r="C6" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="18"/>
+        <v>94</v>
+      </c>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="34"/>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>101</v>
+      <c r="B8" s="38" t="s">
+        <v>95</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="46" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="32"/>
+      <c r="B9" s="23"/>
       <c r="C9" s="12" t="s">
         <v>68</v>
       </c>
@@ -8425,63 +8321,63 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="32"/>
+      <c r="B10" s="23"/>
       <c r="C10" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="32"/>
+      <c r="B11" s="23"/>
       <c r="C11" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="47.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="16" t="s">
-        <v>79</v>
+      <c r="B12" s="23"/>
+      <c r="C12" s="15" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="29"/>
+      <c r="C13" s="34"/>
     </row>
     <row r="14" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="39" t="s">
-        <v>96</v>
+      <c r="B14" s="43" t="s">
+        <v>90</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="29.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="39"/>
+      <c r="B15" s="43"/>
       <c r="C15" s="11" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="39"/>
+      <c r="B16" s="43"/>
       <c r="C16" s="6" t="s">
         <v>58</v>
       </c>
@@ -8490,7 +8386,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="39"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="6" t="s">
         <v>57</v>
       </c>
@@ -8499,37 +8395,37 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="39"/>
+      <c r="B18" s="43"/>
       <c r="C18" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="27.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="6" t="s">
-        <v>69</v>
+        <v>109</v>
+      </c>
+      <c r="B19" s="44"/>
+      <c r="C19" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="29"/>
-    </row>
-    <row r="21" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="34"/>
+    </row>
+    <row r="21" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="27"/>
+      <c r="C21" s="42"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9494,7 +9390,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D954"/>
+  <dimension ref="A1:C950"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6328125" customWidth="1"/>
@@ -9502,21 +9398,21 @@
     <col min="3" max="3" width="48.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -9527,106 +9423,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="41" t="s">
-        <v>147</v>
+      <c r="B4" s="27" t="s">
+        <v>139</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="42"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="42.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="28"/>
+      <c r="C6" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="28"/>
+      <c r="C7" s="18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="42"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="19" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="47" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C9" s="26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10561,16 +10426,12 @@
     <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B4:B12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B4:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>

--- a/media/data/program_ICAAM_2026.xlsx
+++ b/media/data/program_ICAAM_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bahcesehir-my.sharepoint.com/personal/charyyar_ashyralyyev_bau_edu_tr/Documents/Belgeler/Charyyar/Conference/Conference2026/ICAAM2026/Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1067" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F40E0CF-BCEA-4487-9475-69AE35C69B2B}"/>
+  <xr:revisionPtr revIDLastSave="1086" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADF912C1-30EC-4637-AC45-9B3DC5403C88}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="September 26" sheetId="16" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="153">
   <si>
     <t xml:space="preserve">  HALL  Miramor Hotel&amp;Spa</t>
   </si>
@@ -1655,7 +1655,22 @@
     <t>Bakytbek Koshanov,  Alexander Soldatov, Riemann-Hilbert problem for a fourth-order elliptic equation in a quadrant</t>
   </si>
   <si>
-    <t>10.15-10.45</t>
+    <t>10.30-11.00</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gulden Karshygina (Amiran Gogatishvili), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>Universal approach to pointwise and integral estimates in cones of monotone functions</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1963,7 +1978,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2025,13 +2040,54 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2042,48 +2098,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2365,26 +2379,26 @@
     <row r="1" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
     </row>
     <row r="29" spans="1:4" ht="71.150000000000006" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
     </row>
     <row r="31" spans="1:4" ht="47.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2417,18 +2431,18 @@
       <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2445,7 +2459,7 @@
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C5" s="20" t="s">
@@ -2456,7 +2470,7 @@
       <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="39"/>
+      <c r="B6" s="29"/>
       <c r="C6" s="6" t="s">
         <v>89</v>
       </c>
@@ -2465,16 +2479,16 @@
       <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" spans="1:3" ht="77.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="21" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -2485,7 +2499,7 @@
       <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="39"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="15" t="s">
         <v>115</v>
       </c>
@@ -2494,7 +2508,7 @@
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="39"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="15" t="s">
         <v>75</v>
       </c>
@@ -2503,7 +2517,7 @@
       <c r="A11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="39"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="15" t="s">
         <v>76</v>
       </c>
@@ -2512,7 +2526,7 @@
       <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="39"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="15" t="s">
         <v>77</v>
       </c>
@@ -2521,16 +2535,16 @@
       <c r="A13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="27"/>
     </row>
     <row r="14" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="21" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="15" t="s">
@@ -2541,7 +2555,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="39"/>
+      <c r="B15" s="29"/>
       <c r="C15" s="15" t="s">
         <v>73</v>
       </c>
@@ -2550,7 +2564,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="39"/>
+      <c r="B16" s="29"/>
       <c r="C16" s="15" t="s">
         <v>150</v>
       </c>
@@ -2559,7 +2573,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="39"/>
+      <c r="B17" s="29"/>
       <c r="C17" s="15" t="s">
         <v>146</v>
       </c>
@@ -2568,37 +2582,37 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="34"/>
+      <c r="C18" s="27"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="27"/>
     </row>
     <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="41"/>
+      <c r="C20" s="37"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="34"/>
+      <c r="C21" s="27"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3577,18 +3591,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -3605,7 +3619,7 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="21" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -3616,7 +3630,7 @@
       <c r="A5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="39"/>
+      <c r="B5" s="29"/>
       <c r="C5" s="6" t="s">
         <v>105</v>
       </c>
@@ -3625,16 +3639,16 @@
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="34"/>
+      <c r="C6" s="27"/>
     </row>
     <row r="7" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="21" t="s">
         <v>137</v>
       </c>
       <c r="C7" s="16" t="s">
@@ -3645,7 +3659,7 @@
       <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="38"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="16" t="s">
         <v>101</v>
       </c>
@@ -3654,7 +3668,7 @@
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="38"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="6" t="s">
         <v>116</v>
       </c>
@@ -3663,7 +3677,7 @@
       <c r="A10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="38"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="16" t="s">
         <v>102</v>
       </c>
@@ -3672,7 +3686,7 @@
       <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="38"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="16" t="s">
         <v>104</v>
       </c>
@@ -3681,16 +3695,16 @@
       <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="27"/>
     </row>
     <row r="13" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="21" t="s">
         <v>138</v>
       </c>
       <c r="C13" s="16" t="s">
@@ -3701,7 +3715,7 @@
       <c r="A14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="39"/>
+      <c r="B14" s="29"/>
       <c r="C14" s="16" t="s">
         <v>97</v>
       </c>
@@ -3710,7 +3724,7 @@
       <c r="A15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="39"/>
+      <c r="B15" s="29"/>
       <c r="C15" s="16" t="s">
         <v>98</v>
       </c>
@@ -3719,7 +3733,7 @@
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="39"/>
+      <c r="B16" s="29"/>
       <c r="C16" s="16" t="s">
         <v>99</v>
       </c>
@@ -3728,7 +3742,7 @@
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="39"/>
+      <c r="B17" s="29"/>
       <c r="C17" s="16" t="s">
         <v>136</v>
       </c>
@@ -3737,16 +3751,16 @@
       <c r="A18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="34"/>
+      <c r="C18" s="27"/>
     </row>
     <row r="19" spans="1:3" ht="39.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="21" t="s">
         <v>120</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -3757,7 +3771,7 @@
       <c r="A20" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B20" s="39"/>
+      <c r="B20" s="29"/>
       <c r="C20" s="15" t="s">
         <v>142</v>
       </c>
@@ -3766,7 +3780,7 @@
       <c r="A21" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="39"/>
+      <c r="B21" s="29"/>
       <c r="C21" s="19" t="s">
         <v>143</v>
       </c>
@@ -3775,7 +3789,7 @@
       <c r="A22" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="39"/>
+      <c r="B22" s="29"/>
       <c r="C22" s="16" t="s">
         <v>103</v>
       </c>
@@ -3784,7 +3798,7 @@
       <c r="A23" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="39"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="11" t="s">
         <v>149</v>
       </c>
@@ -3793,10 +3807,10 @@
       <c r="A24" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="42"/>
+      <c r="C24" s="22"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4771,18 +4785,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -4799,7 +4813,7 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="21" t="s">
         <v>84</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -4810,7 +4824,7 @@
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="23"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="6" t="s">
         <v>41</v>
       </c>
@@ -4819,7 +4833,7 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="6" t="s">
         <v>42</v>
       </c>
@@ -4828,16 +4842,16 @@
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -4848,7 +4862,7 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="39"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="6" t="s">
         <v>43</v>
       </c>
@@ -4857,7 +4871,7 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="39"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="6" t="s">
         <v>47</v>
       </c>
@@ -4866,7 +4880,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="39"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="6" t="s">
         <v>59</v>
       </c>
@@ -4875,7 +4889,7 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="39"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="6" t="s">
         <v>60</v>
       </c>
@@ -4884,16 +4898,16 @@
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="27"/>
     </row>
     <row r="14" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="21" t="s">
         <v>80</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -4904,7 +4918,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="23"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
@@ -4913,7 +4927,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="23"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="6" t="s">
         <v>49</v>
       </c>
@@ -4922,7 +4936,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="23"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="6" t="s">
         <v>50</v>
       </c>
@@ -4931,7 +4945,7 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="23"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="15" t="s">
         <v>114</v>
       </c>
@@ -4940,19 +4954,19 @@
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="27"/>
     </row>
     <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="42"/>
+      <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5926,18 +5940,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -5954,7 +5968,7 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="21" t="s">
         <v>82</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -5965,7 +5979,7 @@
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="23"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="11" t="s">
         <v>147</v>
       </c>
@@ -5974,7 +5988,7 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="6" t="s">
         <v>62</v>
       </c>
@@ -5983,16 +5997,16 @@
       <c r="A7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="18" t="s">
@@ -6003,7 +6017,7 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="38"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="6" t="s">
         <v>53</v>
       </c>
@@ -6012,7 +6026,7 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="38"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="6" t="s">
         <v>52</v>
       </c>
@@ -6021,7 +6035,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="38"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="6" t="s">
         <v>56</v>
       </c>
@@ -6030,23 +6044,23 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="38"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="11"/>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="27"/>
     </row>
     <row r="14" spans="1:3" ht="42.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -6057,7 +6071,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="38"/>
+      <c r="B15" s="21"/>
       <c r="C15" s="2" t="s">
         <v>65</v>
       </c>
@@ -6066,7 +6080,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="38"/>
+      <c r="B16" s="21"/>
       <c r="C16" s="2" t="s">
         <v>66</v>
       </c>
@@ -6075,7 +6089,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="38"/>
+      <c r="B17" s="21"/>
       <c r="C17" s="12" t="s">
         <v>61</v>
       </c>
@@ -6084,7 +6098,7 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="38"/>
+      <c r="B18" s="21"/>
       <c r="C18" s="12" t="s">
         <v>93</v>
       </c>
@@ -6093,19 +6107,19 @@
       <c r="A19" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="27"/>
     </row>
     <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="42"/>
+      <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7079,18 +7093,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -7107,7 +7121,7 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -7118,7 +7132,7 @@
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="23"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="6" t="s">
         <v>64</v>
       </c>
@@ -7127,7 +7141,7 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="12" t="s">
         <v>67</v>
       </c>
@@ -7136,16 +7150,16 @@
       <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="21" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -7156,7 +7170,7 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="39"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="2" t="s">
         <v>63</v>
       </c>
@@ -7165,7 +7179,7 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="39"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="2" t="s">
         <v>112</v>
       </c>
@@ -7174,7 +7188,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="39"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="2" t="s">
         <v>45</v>
       </c>
@@ -7183,7 +7197,7 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="39"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="2" t="s">
         <v>118</v>
       </c>
@@ -7192,16 +7206,16 @@
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="27"/>
     </row>
     <row r="14" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="21" t="s">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -7212,7 +7226,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="23"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="2" t="s">
         <v>69</v>
       </c>
@@ -7221,7 +7235,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="23"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="2" t="s">
         <v>44</v>
       </c>
@@ -7230,7 +7244,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="23"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="2" t="s">
         <v>108</v>
       </c>
@@ -7239,7 +7253,7 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="23"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="12" t="s">
         <v>70</v>
       </c>
@@ -7248,19 +7262,19 @@
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="27"/>
     </row>
     <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="42"/>
+      <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8234,18 +8248,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -8262,7 +8276,7 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="21" t="s">
         <v>83</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -8273,7 +8287,7 @@
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="23"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="6" t="s">
         <v>107</v>
       </c>
@@ -8282,7 +8296,7 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="12" t="s">
         <v>94</v>
       </c>
@@ -8292,16 +8306,16 @@
       <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8312,7 +8326,7 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="23"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="12" t="s">
         <v>68</v>
       </c>
@@ -8321,7 +8335,7 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="23"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="6" t="s">
         <v>111</v>
       </c>
@@ -8330,7 +8344,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="23"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="6" t="s">
         <v>124</v>
       </c>
@@ -8339,7 +8353,7 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="23"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="15" t="s">
         <v>74</v>
       </c>
@@ -8348,16 +8362,16 @@
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="27"/>
     </row>
     <row r="14" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="38" t="s">
         <v>90</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -8368,7 +8382,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="43"/>
+      <c r="B15" s="38"/>
       <c r="C15" s="11" t="s">
         <v>148</v>
       </c>
@@ -8377,7 +8391,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="43"/>
+      <c r="B16" s="38"/>
       <c r="C16" s="6" t="s">
         <v>58</v>
       </c>
@@ -8386,7 +8400,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="43"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="6" t="s">
         <v>57</v>
       </c>
@@ -8395,7 +8409,7 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="43"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="2" t="s">
         <v>46</v>
       </c>
@@ -8404,7 +8418,7 @@
       <c r="A19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="44"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="2" t="s">
         <v>121</v>
       </c>
@@ -8413,19 +8427,19 @@
       <c r="A20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="34"/>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="42"/>
+      <c r="C21" s="22"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9399,18 +9413,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -9427,7 +9441,7 @@
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="42" t="s">
         <v>139</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -9438,7 +9452,7 @@
       <c r="A5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="43"/>
       <c r="C5" s="12" t="s">
         <v>92</v>
       </c>
@@ -9447,44 +9461,48 @@
       <c r="A6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="28"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="41" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="18" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="28"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="43" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C10" s="41" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10430,8 +10448,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B4:B9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>

--- a/media/data/program_ICAAM_2026.xlsx
+++ b/media/data/program_ICAAM_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bahcesehir-my.sharepoint.com/personal/charyyar_ashyralyyev_bau_edu_tr/Documents/Belgeler/Charyyar/Conference/Conference2026/ICAAM2026/Program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1086" documentId="8_{AA0175ED-2FD3-44DA-9ED6-C176C9CA5FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADF912C1-30EC-4637-AC45-9B3DC5403C88}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{305578DD-7651-478B-A127-B50A17EA27AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="September 26" sheetId="16" r:id="rId1"/>
@@ -1454,20 +1454,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Robyn Irawan (Indonesia)  (Benny Yong, Erin Andrea Ramadhani Pramono, Neilshan Loedy, Farah Kristiani) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Age-structured Bayesian SIR modelling with reversible-jump MCMC: a comparative study of two social contact matrix projections </t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Invited Speaker:  Prof. Dr. Alexander L. Skubachevskii (Russia), </t>
     </r>
     <r>
@@ -1670,6 +1656,20 @@
         <charset val="162"/>
       </rPr>
       <t>Universal approach to pointwise and integral estimates in cones of monotone functions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Robyn Irawan (Indonesia)  (Benny Yong, Erin Andrea Ramadhani Pramono, Farah Kristiani) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Age-structured Bayesian SIR modelling with reversible-jump MCMC: a comparative study of two social contact matrix projections </t>
     </r>
   </si>
 </sst>
@@ -2040,27 +2040,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2071,16 +2074,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2169,6 +2169,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2379,26 +2383,26 @@
     <row r="1" spans="1:3" ht="86.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:3" ht="34" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
     </row>
     <row r="29" spans="1:4" ht="71.150000000000006" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
     </row>
     <row r="31" spans="1:4" ht="47.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
+      <c r="A31" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2431,18 +2435,18 @@
       <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2459,18 +2463,18 @@
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="27" t="s">
         <v>95</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="29"/>
+      <c r="B6" s="28"/>
       <c r="C6" s="6" t="s">
         <v>89</v>
       </c>
@@ -2479,27 +2483,27 @@
       <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="22"/>
     </row>
     <row r="8" spans="1:3" ht="77.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="27" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="41.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="29"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="15" t="s">
         <v>115</v>
       </c>
@@ -2508,7 +2512,7 @@
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="29"/>
+      <c r="B10" s="28"/>
       <c r="C10" s="15" t="s">
         <v>75</v>
       </c>
@@ -2517,7 +2521,7 @@
       <c r="A11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="29"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="15" t="s">
         <v>76</v>
       </c>
@@ -2526,7 +2530,7 @@
       <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="29"/>
+      <c r="B12" s="28"/>
       <c r="C12" s="15" t="s">
         <v>77</v>
       </c>
@@ -2535,16 +2539,16 @@
       <c r="A13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="27"/>
+      <c r="C13" s="22"/>
     </row>
     <row r="14" spans="1:3" ht="41.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="27" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="15" t="s">
@@ -2555,7 +2559,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="29"/>
+      <c r="B15" s="28"/>
       <c r="C15" s="15" t="s">
         <v>73</v>
       </c>
@@ -2564,55 +2568,55 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="29"/>
+      <c r="B16" s="28"/>
       <c r="C16" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="29"/>
+      <c r="B17" s="28"/>
       <c r="C17" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="27"/>
+      <c r="C18" s="22"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="27"/>
+      <c r="C19" s="22"/>
     </row>
     <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="30"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="27"/>
+      <c r="C21" s="22"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3591,18 +3595,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -3619,18 +3623,18 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="27" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="29"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="6" t="s">
         <v>105</v>
       </c>
@@ -3639,17 +3643,17 @@
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="22"/>
     </row>
     <row r="7" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>137</v>
+      <c r="B7" s="27" t="s">
+        <v>136</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>100</v>
@@ -3659,7 +3663,7 @@
       <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="21"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="16" t="s">
         <v>101</v>
       </c>
@@ -3668,7 +3672,7 @@
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="21"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="6" t="s">
         <v>116</v>
       </c>
@@ -3677,7 +3681,7 @@
       <c r="A10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="21"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="16" t="s">
         <v>102</v>
       </c>
@@ -3686,7 +3690,7 @@
       <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="16" t="s">
         <v>104</v>
       </c>
@@ -3695,17 +3699,17 @@
       <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="27"/>
+      <c r="C12" s="22"/>
     </row>
     <row r="13" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="21" t="s">
-        <v>138</v>
+      <c r="B13" s="27" t="s">
+        <v>137</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>96</v>
@@ -3715,7 +3719,7 @@
       <c r="A14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="29"/>
+      <c r="B14" s="28"/>
       <c r="C14" s="16" t="s">
         <v>97</v>
       </c>
@@ -3724,7 +3728,7 @@
       <c r="A15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="29"/>
+      <c r="B15" s="28"/>
       <c r="C15" s="16" t="s">
         <v>98</v>
       </c>
@@ -3733,7 +3737,7 @@
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="29"/>
+      <c r="B16" s="28"/>
       <c r="C16" s="16" t="s">
         <v>99</v>
       </c>
@@ -3742,25 +3746,25 @@
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="29"/>
+      <c r="B17" s="28"/>
       <c r="C17" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B18" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="27"/>
+      <c r="C18" s="22"/>
     </row>
     <row r="19" spans="1:3" ht="39.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>120</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -3769,48 +3773,48 @@
     </row>
     <row r="20" spans="1:3" ht="39.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B20" s="29"/>
+        <v>132</v>
+      </c>
+      <c r="B20" s="28"/>
       <c r="C20" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="29"/>
+        <v>133</v>
+      </c>
+      <c r="B21" s="28"/>
       <c r="C21" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="38.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="29"/>
+        <v>134</v>
+      </c>
+      <c r="B22" s="28"/>
       <c r="C22" s="16" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" s="29"/>
+        <v>139</v>
+      </c>
+      <c r="B23" s="28"/>
       <c r="C23" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B24" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="37"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4785,18 +4789,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -4813,7 +4817,7 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="27" t="s">
         <v>84</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -4824,7 +4828,7 @@
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="24"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="6" t="s">
         <v>41</v>
       </c>
@@ -4833,7 +4837,7 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="25"/>
       <c r="C6" s="6" t="s">
         <v>42</v>
       </c>
@@ -4842,16 +4846,16 @@
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="22"/>
     </row>
     <row r="8" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="27" t="s">
         <v>90</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -4862,7 +4866,7 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="29"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="6" t="s">
         <v>43</v>
       </c>
@@ -4871,7 +4875,7 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="29"/>
+      <c r="B10" s="28"/>
       <c r="C10" s="6" t="s">
         <v>47</v>
       </c>
@@ -4880,7 +4884,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="29"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="6" t="s">
         <v>59</v>
       </c>
@@ -4889,7 +4893,7 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="29"/>
+      <c r="B12" s="28"/>
       <c r="C12" s="6" t="s">
         <v>60</v>
       </c>
@@ -4898,16 +4902,16 @@
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="27"/>
+      <c r="C13" s="22"/>
     </row>
     <row r="14" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="27" t="s">
         <v>80</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -4918,7 +4922,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="24"/>
+      <c r="B15" s="25"/>
       <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
@@ -4927,7 +4931,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="24"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="6" t="s">
         <v>49</v>
       </c>
@@ -4936,7 +4940,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="24"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="6" t="s">
         <v>50</v>
       </c>
@@ -4945,7 +4949,7 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="15" t="s">
         <v>114</v>
       </c>
@@ -4954,19 +4958,19 @@
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="27"/>
+      <c r="C19" s="22"/>
     </row>
     <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="22"/>
+      <c r="C20" s="37"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5940,18 +5944,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -5968,7 +5972,7 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="27" t="s">
         <v>82</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -5979,16 +5983,16 @@
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="24"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="25"/>
       <c r="C6" s="6" t="s">
         <v>62</v>
       </c>
@@ -5997,16 +6001,16 @@
       <c r="A7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="22"/>
     </row>
     <row r="8" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="27" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="18" t="s">
@@ -6017,7 +6021,7 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="21"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="6" t="s">
         <v>53</v>
       </c>
@@ -6026,7 +6030,7 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="21"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="6" t="s">
         <v>52</v>
       </c>
@@ -6035,7 +6039,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="6" t="s">
         <v>56</v>
       </c>
@@ -6044,23 +6048,23 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="11"/>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="27"/>
+      <c r="C13" s="22"/>
     </row>
     <row r="14" spans="1:3" ht="42.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="27" t="s">
         <v>128</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -6071,7 +6075,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="21"/>
+      <c r="B15" s="27"/>
       <c r="C15" s="2" t="s">
         <v>65</v>
       </c>
@@ -6080,7 +6084,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="21"/>
+      <c r="B16" s="27"/>
       <c r="C16" s="2" t="s">
         <v>66</v>
       </c>
@@ -6089,7 +6093,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="21"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="12" t="s">
         <v>61</v>
       </c>
@@ -6098,7 +6102,7 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="21"/>
+      <c r="B18" s="27"/>
       <c r="C18" s="12" t="s">
         <v>93</v>
       </c>
@@ -6107,19 +6111,19 @@
       <c r="A19" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="27"/>
+      <c r="C19" s="22"/>
     </row>
     <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="22"/>
+      <c r="C20" s="37"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7093,18 +7097,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -7121,7 +7125,7 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="27" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -7132,7 +7136,7 @@
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="24"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="6" t="s">
         <v>64</v>
       </c>
@@ -7141,7 +7145,7 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="25"/>
       <c r="C6" s="12" t="s">
         <v>67</v>
       </c>
@@ -7150,16 +7154,16 @@
       <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="22"/>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -7170,7 +7174,7 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="29"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="2" t="s">
         <v>63</v>
       </c>
@@ -7179,7 +7183,7 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="29"/>
+      <c r="B10" s="28"/>
       <c r="C10" s="2" t="s">
         <v>112</v>
       </c>
@@ -7188,7 +7192,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="29"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="2" t="s">
         <v>45</v>
       </c>
@@ -7197,7 +7201,7 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="29"/>
+      <c r="B12" s="28"/>
       <c r="C12" s="2" t="s">
         <v>118</v>
       </c>
@@ -7206,16 +7210,16 @@
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="27"/>
+      <c r="C13" s="22"/>
     </row>
     <row r="14" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="27" t="s">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -7226,7 +7230,7 @@
       <c r="A15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="24"/>
+      <c r="B15" s="25"/>
       <c r="C15" s="2" t="s">
         <v>69</v>
       </c>
@@ -7235,7 +7239,7 @@
       <c r="A16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="24"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="2" t="s">
         <v>44</v>
       </c>
@@ -7244,7 +7248,7 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="24"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="2" t="s">
         <v>108</v>
       </c>
@@ -7253,7 +7257,7 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="12" t="s">
         <v>70</v>
       </c>
@@ -7262,19 +7266,19 @@
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="27"/>
+      <c r="C19" s="22"/>
     </row>
     <row r="20" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="22"/>
+      <c r="C20" s="37"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8248,18 +8252,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -8276,7 +8280,7 @@
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="27" t="s">
         <v>83</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -8287,7 +8291,7 @@
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="24"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="6" t="s">
         <v>107</v>
       </c>
@@ -8296,7 +8300,7 @@
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="25"/>
       <c r="C6" s="12" t="s">
         <v>94</v>
       </c>
@@ -8306,16 +8310,16 @@
       <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="22"/>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="27" t="s">
         <v>95</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -8326,7 +8330,7 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="24"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="12" t="s">
         <v>68</v>
       </c>
@@ -8335,7 +8339,7 @@
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="6" t="s">
         <v>111</v>
       </c>
@@ -8344,7 +8348,7 @@
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="24"/>
+      <c r="B11" s="25"/>
       <c r="C11" s="6" t="s">
         <v>124</v>
       </c>
@@ -8353,7 +8357,7 @@
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="24"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="15" t="s">
         <v>74</v>
       </c>
@@ -8362,10 +8366,10 @@
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="27"/>
+      <c r="C13" s="22"/>
     </row>
     <row r="14" spans="1:4" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -8384,7 +8388,7 @@
       </c>
       <c r="B15" s="38"/>
       <c r="C15" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8425,21 +8429,21 @@
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="27"/>
+      <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:3" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9413,18 +9417,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -9442,7 +9446,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>91</v>
@@ -9490,12 +9494,12 @@
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>20</v>
